--- a/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
+++ b/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpenev/projects/git/CircularizationDissipationConstraints/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CCB290-719C-7744-98BB-C41CD46E0DFF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64123CA-8ED9-0A4F-AFF2-D3A4171914AE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15940" yWindow="5380" windowWidth="31560" windowHeight="22480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="104">
   <si>
     <t>#</t>
   </si>
@@ -317,13 +317,28 @@
   </si>
   <si>
     <t>Q=const</t>
+  </si>
+  <si>
+    <t>bold purple</t>
+  </si>
+  <si>
+    <t>Stellar mass distributions go out of range too often</t>
+  </si>
+  <si>
+    <t>kartof</t>
+  </si>
+  <si>
+    <t>ganymede</t>
+  </si>
+  <si>
+    <t>stampede</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -481,6 +496,14 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFD261CE"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -851,7 +874,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -865,6 +888,8 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -912,6 +937,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFD261CE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1220,7 +1250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V154"/>
+  <dimension ref="A1:V155"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -1605,1376 +1635,1374 @@
       <c r="C73" s="4"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" t="s">
+        <v>100</v>
+      </c>
+      <c r="C74" s="4"/>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A75" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
         <v>96</v>
       </c>
-      <c r="C74" s="4"/>
-    </row>
-    <row r="75" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="2" t="s">
+      <c r="C75" s="4"/>
+    </row>
+    <row r="76" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B76" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="F76" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H75" s="2" t="s">
+      <c r="H76" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I75" s="2" t="s">
+      <c r="I76" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J75" s="2" t="s">
+      <c r="J76" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="K76" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L75" s="2" t="s">
+      <c r="L76" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M75" s="2" t="s">
+      <c r="M76" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N75" s="2" t="s">
+      <c r="N76" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="O75" s="2" t="s">
+      <c r="O76" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="P75" s="2" t="s">
+      <c r="P76" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="Q75" s="2" t="s">
+      <c r="Q76" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="R75" s="2" t="s">
+      <c r="R76" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="S75" s="2" t="s">
+      <c r="S76" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="T75" s="2" t="s">
+      <c r="T76" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="U75" s="2" t="s">
+      <c r="U76" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C76" s="2" t="s">
+    <row r="77" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C77" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G77" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="H77" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I76" s="2" t="s">
+      <c r="I77" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J76" s="2" t="s">
+      <c r="J77" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="K77" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L76" s="2" t="s">
+      <c r="L77" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="M76" s="2" t="s">
+      <c r="M77" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="N76" s="2" t="s">
+      <c r="N77" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="O76" s="2" t="s">
+      <c r="O77" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="P76" s="2" t="s">
+      <c r="P77" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q76" s="2" t="s">
+      <c r="Q77" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="R76" s="2" t="s">
+      <c r="R77" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="S76" s="2" t="s">
+      <c r="S77" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="T76" s="2" t="s">
+      <c r="T77" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="U76" s="2" t="s">
+      <c r="U77" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="V76" s="2" t="s">
+      <c r="V77" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C77">
+    <row r="78" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C78" s="13">
         <v>25011</v>
       </c>
-      <c r="D77">
+      <c r="D78" s="13">
         <v>1.574695</v>
       </c>
-      <c r="E77">
+      <c r="E78" s="13">
         <v>5.0000000000000004E-6</v>
       </c>
-      <c r="F77">
+      <c r="F78" s="13">
         <v>1947.6</v>
       </c>
-      <c r="G77">
+      <c r="G78" s="13">
         <v>1.47</v>
       </c>
-      <c r="H77">
+      <c r="H78" s="13">
         <v>0.24</v>
       </c>
-      <c r="I77">
+      <c r="I78" s="13">
         <v>31.3</v>
       </c>
-      <c r="J77">
+      <c r="J78" s="13">
         <v>0.4</v>
       </c>
-      <c r="K77">
+      <c r="K78" s="13">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="L77">
+      <c r="L78" s="13">
         <v>0.01</v>
       </c>
-      <c r="M77">
+      <c r="M78" s="13">
         <v>140</v>
       </c>
-      <c r="N77">
+      <c r="N78" s="13">
         <v>90</v>
       </c>
-      <c r="O77">
+      <c r="O78" s="13">
         <v>54467.8</v>
       </c>
-      <c r="P77">
+      <c r="P78" s="13">
         <v>0.4</v>
       </c>
-      <c r="Q77">
+      <c r="Q78" s="13">
         <v>0.67700000000000005</v>
       </c>
-      <c r="R77">
+      <c r="R78" s="13">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="S77" s="1">
+      <c r="S78" s="14">
         <v>4.9899999999999996E-3</v>
       </c>
-      <c r="T77" s="1">
+      <c r="T78" s="14">
         <v>1.7000000000000001E-4</v>
       </c>
-      <c r="U77">
+      <c r="U78" s="13">
         <v>1.36</v>
       </c>
-      <c r="V77">
+      <c r="V78" s="13">
         <v>33</v>
       </c>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C78">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A79" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C79">
         <v>49002</v>
       </c>
-      <c r="D78">
+      <c r="D79">
         <v>1.6159159999999999</v>
       </c>
-      <c r="E78">
+      <c r="E79">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F78">
+      <c r="F79">
         <v>1573.2</v>
       </c>
-      <c r="G78">
+      <c r="G79">
         <v>3.8</v>
       </c>
-      <c r="H78">
+      <c r="H79">
         <v>0.8</v>
       </c>
-      <c r="I78">
+      <c r="I79">
         <v>53.7</v>
       </c>
-      <c r="J78">
+      <c r="J79">
         <v>1.2</v>
       </c>
-      <c r="K78">
+      <c r="K79">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="L78">
+      <c r="L79">
         <v>0.02</v>
       </c>
-      <c r="M78">
+      <c r="M79">
         <v>240</v>
       </c>
-      <c r="N78">
+      <c r="N79">
         <v>60</v>
       </c>
-      <c r="O78">
+      <c r="O79">
         <v>53897.1</v>
       </c>
-      <c r="P78">
+      <c r="P79">
         <v>0.3</v>
       </c>
-      <c r="Q78">
+      <c r="Q79">
         <v>1.19</v>
       </c>
-      <c r="R78">
+      <c r="R79">
         <v>0.03</v>
       </c>
-      <c r="S78" s="1">
+      <c r="S79" s="1">
         <v>2.5899999999999999E-2</v>
       </c>
-      <c r="T78" s="1">
+      <c r="T79" s="1">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="U78">
+      <c r="U79">
         <v>3.18</v>
       </c>
-      <c r="V78">
+      <c r="V79">
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C79" s="11">
+    <row r="80" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C80" s="11">
         <v>14008</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D80" s="11">
         <v>1.71953</v>
       </c>
-      <c r="E79" s="11">
+      <c r="E80" s="11">
         <v>2.4000000000000001E-5</v>
       </c>
-      <c r="F79" s="11">
+      <c r="F80" s="11">
         <v>860</v>
       </c>
-      <c r="G79" s="11">
+      <c r="G80" s="11">
         <v>2.6</v>
       </c>
-      <c r="H79" s="11">
+      <c r="H80" s="11">
         <v>0.9</v>
       </c>
-      <c r="I79" s="11">
+      <c r="I80" s="11">
         <v>45.3</v>
       </c>
-      <c r="J79" s="11">
+      <c r="J80" s="11">
         <v>1.3</v>
       </c>
-      <c r="K79" s="11">
+      <c r="K80" s="11">
         <v>0.02</v>
       </c>
-      <c r="L79" s="11">
+      <c r="L80" s="11">
         <v>0.03</v>
       </c>
-      <c r="M79" s="11">
+      <c r="M80" s="11">
         <v>300</v>
       </c>
-      <c r="N79" s="11">
+      <c r="N80" s="11">
         <v>80</v>
       </c>
-      <c r="O79" s="11">
+      <c r="O80" s="11">
         <v>52959.5</v>
       </c>
-      <c r="P79" s="11">
+      <c r="P80" s="11">
         <v>0.4</v>
       </c>
-      <c r="Q79" s="11">
+      <c r="Q80" s="11">
         <v>1.07</v>
       </c>
-      <c r="R79" s="11">
+      <c r="R80" s="11">
         <v>0.03</v>
       </c>
-      <c r="S79" s="12">
+      <c r="S80" s="12">
         <v>1.66E-2</v>
       </c>
-      <c r="T79" s="12">
+      <c r="T80" s="12">
         <v>1.5E-3</v>
       </c>
-      <c r="U79" s="11">
+      <c r="U80" s="11">
         <v>2.93</v>
       </c>
-      <c r="V79" s="11">
+      <c r="V80" s="11">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C80">
+    <row r="81" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" s="13">
         <v>32006</v>
       </c>
-      <c r="D80">
+      <c r="D81" s="13">
         <v>1.8471599999999999</v>
       </c>
-      <c r="E80">
+      <c r="E81" s="13">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="F80">
+      <c r="F81" s="13">
         <v>2623.5</v>
       </c>
-      <c r="G80">
+      <c r="G81" s="13">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H80">
+      <c r="H81" s="13">
         <v>0.3</v>
       </c>
-      <c r="I80">
+      <c r="I81" s="13">
         <v>18.2</v>
       </c>
-      <c r="J80">
+      <c r="J81" s="13">
         <v>0.3</v>
       </c>
-      <c r="K80">
+      <c r="K81" s="13">
         <v>0.05</v>
       </c>
-      <c r="L80">
+      <c r="L81" s="13">
         <v>0.03</v>
       </c>
-      <c r="M80">
+      <c r="M81" s="13">
         <v>330</v>
       </c>
-      <c r="N80">
+      <c r="N81" s="13">
         <v>30</v>
       </c>
-      <c r="O80">
+      <c r="O81" s="13">
         <v>52305.65</v>
       </c>
-      <c r="P80">
+      <c r="P81" s="13">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Q80">
+      <c r="Q81" s="13">
         <v>0.46200000000000002</v>
       </c>
-      <c r="R80">
+      <c r="R81" s="13">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="S80" s="1">
+      <c r="S81" s="13">
         <v>1.15E-3</v>
       </c>
-      <c r="T80" s="1">
+      <c r="T81" s="13">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="U80">
+      <c r="U81" s="13">
         <v>1.08</v>
       </c>
-      <c r="V80">
+      <c r="V81" s="13">
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="C81">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A82" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C82">
         <v>66004</v>
       </c>
-      <c r="D81">
+      <c r="D82">
         <v>2.277936</v>
       </c>
-      <c r="E81">
+      <c r="E82">
         <v>1.5E-5</v>
       </c>
-      <c r="F81">
+      <c r="F82">
         <v>1324.8</v>
       </c>
-      <c r="G81">
+      <c r="G82">
         <v>2.9</v>
       </c>
-      <c r="H81">
+      <c r="H82">
         <v>0.5</v>
       </c>
-      <c r="I81">
+      <c r="I82">
         <v>38.6</v>
       </c>
-      <c r="J81">
+      <c r="J82">
         <v>0.7</v>
       </c>
-      <c r="K81">
+      <c r="K82">
         <v>1.6E-2</v>
       </c>
-      <c r="L81">
+      <c r="L82">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="M81">
+      <c r="M82">
         <v>150</v>
       </c>
-      <c r="N81">
+      <c r="N82">
         <v>70</v>
       </c>
-      <c r="O81">
+      <c r="O82">
         <v>53178.6</v>
       </c>
-      <c r="P81">
+      <c r="P82">
         <v>0.5</v>
       </c>
-      <c r="Q81">
+      <c r="Q82">
         <v>1.208</v>
       </c>
-      <c r="R81">
+      <c r="R82">
         <v>2.3E-2</v>
       </c>
-      <c r="S81" s="1">
+      <c r="S82" s="1">
         <v>1.35E-2</v>
       </c>
-      <c r="T81" s="1">
+      <c r="T82" s="1">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="U81">
+      <c r="U82">
         <v>1.8</v>
       </c>
-      <c r="V81">
+      <c r="V82">
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="C82">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A83" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83">
         <v>13001</v>
       </c>
-      <c r="D82">
+      <c r="D83">
         <v>4.2407899999999996</v>
       </c>
-      <c r="E82">
+      <c r="E83">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="F82">
+      <c r="F83">
         <v>871</v>
       </c>
-      <c r="G82">
+      <c r="G83">
         <v>2.7</v>
       </c>
-      <c r="H82">
+      <c r="H83">
         <v>0.6</v>
       </c>
-      <c r="I82">
+      <c r="I83">
         <v>55.1</v>
       </c>
-      <c r="J82">
+      <c r="J83">
         <v>1</v>
       </c>
-      <c r="K82">
+      <c r="K83">
         <v>4.7E-2</v>
       </c>
-      <c r="L82">
+      <c r="L83">
         <v>0.02</v>
       </c>
-      <c r="M82">
+      <c r="M83">
         <v>205</v>
       </c>
-      <c r="N82">
+      <c r="N83">
         <v>20</v>
       </c>
-      <c r="O82">
+      <c r="O83">
         <v>54002.05</v>
       </c>
-      <c r="P82">
+      <c r="P83">
         <v>0.24</v>
       </c>
-      <c r="Q82">
+      <c r="Q83">
         <v>3.21</v>
       </c>
-      <c r="R82">
+      <c r="R83">
         <v>0.06</v>
       </c>
-      <c r="S82" s="1">
+      <c r="S83" s="1">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="T82" s="1">
+      <c r="T83" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="U82">
+      <c r="U83">
         <v>2.4300000000000002</v>
       </c>
-      <c r="V82">
+      <c r="V83">
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="3:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C83" s="11">
+    <row r="84" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B84"/>
+      <c r="C84" s="11">
         <v>35025</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D84" s="11">
         <v>4.6412300000000002</v>
       </c>
-      <c r="E83" s="11">
+      <c r="E84" s="11">
         <v>1.2999999999999999E-4</v>
       </c>
-      <c r="F83" s="11">
+      <c r="F84" s="11">
         <v>199.4</v>
       </c>
-      <c r="G83" s="11">
+      <c r="G84" s="11">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H83" s="11">
+      <c r="H84" s="11">
         <v>0.22</v>
       </c>
-      <c r="I83" s="11">
+      <c r="I84" s="11">
         <v>39.200000000000003</v>
       </c>
-      <c r="J83" s="11">
+      <c r="J84" s="11">
         <v>0.5</v>
       </c>
-      <c r="K83" s="11">
+      <c r="K84" s="11">
         <v>0.20799999999999999</v>
       </c>
-      <c r="L83" s="11">
+      <c r="L84" s="11">
         <v>1.2E-2</v>
       </c>
-      <c r="M83" s="11">
+      <c r="M84" s="11">
         <v>117.2</v>
       </c>
-      <c r="N83" s="11">
+      <c r="N84" s="11">
         <v>2.4</v>
       </c>
-      <c r="O83" s="11">
+      <c r="O84" s="11">
         <v>51999.66</v>
       </c>
-      <c r="P83" s="11">
+      <c r="P84" s="11">
         <v>0.03</v>
       </c>
-      <c r="Q83" s="11">
+      <c r="Q84" s="11">
         <v>2.4500000000000002</v>
       </c>
-      <c r="R83" s="11">
+      <c r="R84" s="11">
         <v>0.03</v>
       </c>
-      <c r="S83" s="12">
+      <c r="S84" s="12">
         <v>2.7099999999999999E-2</v>
       </c>
-      <c r="T83" s="12">
+      <c r="T84" s="12">
         <v>1E-3</v>
       </c>
-      <c r="U83" s="11">
+      <c r="U84" s="11">
         <v>0.74</v>
       </c>
-      <c r="V83" s="11">
+      <c r="V84" s="11">
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="C84">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A85" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C85">
         <v>60006</v>
       </c>
-      <c r="D84">
+      <c r="D85">
         <v>7.8430999999999997</v>
       </c>
-      <c r="E84">
+      <c r="E85">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F84">
+      <c r="F85">
         <v>153.19999999999999</v>
       </c>
-      <c r="G84">
+      <c r="G85">
         <v>1.9</v>
       </c>
-      <c r="H84">
+      <c r="H85">
         <v>0.3</v>
       </c>
-      <c r="I84">
+      <c r="I85">
         <v>33.14</v>
-      </c>
-      <c r="J84">
-        <v>0.22</v>
-      </c>
-      <c r="K84">
-        <v>1.9E-2</v>
-      </c>
-      <c r="L84">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="M84">
-        <v>319</v>
-      </c>
-      <c r="N84">
-        <v>21</v>
-      </c>
-      <c r="O84">
-        <v>51728.800000000003</v>
-      </c>
-      <c r="P84">
-        <v>0.5</v>
-      </c>
-      <c r="Q84">
-        <v>3.5739999999999998</v>
-      </c>
-      <c r="R84">
-        <v>2.4E-2</v>
-      </c>
-      <c r="S84" s="1">
-        <v>2.9600000000000001E-2</v>
-      </c>
-      <c r="T84" s="1">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="U84">
-        <v>0.66</v>
-      </c>
-      <c r="V84">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="C85">
-        <v>57004</v>
-      </c>
-      <c r="D85">
-        <v>9.1537000000000006</v>
-      </c>
-      <c r="E85">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F85">
-        <v>128.4</v>
-      </c>
-      <c r="G85">
-        <v>3.4</v>
-      </c>
-      <c r="H85">
-        <v>0.18</v>
-      </c>
-      <c r="I85">
-        <v>40.03</v>
       </c>
       <c r="J85">
         <v>0.22</v>
       </c>
       <c r="K85">
+        <v>1.9E-2</v>
+      </c>
+      <c r="L85">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="M85">
+        <v>319</v>
+      </c>
+      <c r="N85">
+        <v>21</v>
+      </c>
+      <c r="O85">
+        <v>51728.800000000003</v>
+      </c>
+      <c r="P85">
+        <v>0.5</v>
+      </c>
+      <c r="Q85">
+        <v>3.5739999999999998</v>
+      </c>
+      <c r="R85">
+        <v>2.4E-2</v>
+      </c>
+      <c r="S85" s="1">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="T85" s="1">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="U85">
+        <v>0.66</v>
+      </c>
+      <c r="V85">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A86" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C86">
+        <v>57004</v>
+      </c>
+      <c r="D86">
+        <v>9.1537000000000006</v>
+      </c>
+      <c r="E86">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F86">
+        <v>128.4</v>
+      </c>
+      <c r="G86">
+        <v>3.4</v>
+      </c>
+      <c r="H86">
+        <v>0.18</v>
+      </c>
+      <c r="I86">
+        <v>40.03</v>
+      </c>
+      <c r="J86">
+        <v>0.22</v>
+      </c>
+      <c r="K86">
         <v>0.123</v>
       </c>
-      <c r="L85">
+      <c r="L86">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="M85">
+      <c r="M86">
         <v>59.3</v>
       </c>
-      <c r="N85">
+      <c r="N86">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O85">
+      <c r="O86">
         <v>56052.14</v>
       </c>
-      <c r="P85">
+      <c r="P86">
         <v>0.06</v>
       </c>
-      <c r="Q85">
+      <c r="Q86">
         <v>5</v>
       </c>
-      <c r="R85">
+      <c r="R86">
         <v>0.03</v>
       </c>
-      <c r="S85" s="1">
+      <c r="S86" s="1">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="T85" s="1">
+      <c r="T86" s="1">
         <v>1E-3</v>
       </c>
-      <c r="U85">
+      <c r="U86">
         <v>0.47</v>
       </c>
-      <c r="V85">
+      <c r="V86">
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="C86">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B87" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C87">
         <v>33002</v>
       </c>
-      <c r="D86">
+      <c r="D87">
         <v>10.9025</v>
       </c>
-      <c r="E86">
+      <c r="E87">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="F86">
+      <c r="F87">
         <v>232.3</v>
       </c>
-      <c r="G86">
+      <c r="G87">
         <v>3.1</v>
       </c>
-      <c r="H86">
+      <c r="H87">
         <v>0.5</v>
       </c>
-      <c r="I86">
+      <c r="I87">
         <v>40.5</v>
       </c>
-      <c r="J86">
+      <c r="J87">
         <v>0.5</v>
       </c>
-      <c r="K86">
+      <c r="K87">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="L86">
+      <c r="L87">
         <v>1.6E-2</v>
       </c>
-      <c r="M86">
+      <c r="M87">
         <v>10</v>
       </c>
-      <c r="N86">
+      <c r="N87">
         <v>30</v>
       </c>
-      <c r="O86">
+      <c r="O87">
         <v>54194.1</v>
       </c>
-      <c r="P86">
+      <c r="P87">
         <v>1</v>
       </c>
-      <c r="Q86">
+      <c r="Q87">
         <v>6.07</v>
       </c>
-      <c r="R86">
+      <c r="R87">
         <v>0.08</v>
       </c>
-      <c r="S86" s="1">
+      <c r="S87" s="1">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="T86" s="1">
+      <c r="T87" s="1">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="U86">
+      <c r="U87">
         <v>1.56</v>
       </c>
-      <c r="V86">
+      <c r="V87">
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C87" s="9">
+    <row r="88" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B88"/>
+      <c r="C88" s="9">
         <v>46013</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D88" s="9">
         <v>14.2111</v>
       </c>
-      <c r="E87" s="9">
+      <c r="E88" s="9">
         <v>1.5E-3</v>
       </c>
-      <c r="F87" s="9">
+      <c r="F88" s="9">
         <v>105.4</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G88" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H87" s="9">
+      <c r="H88" s="9">
         <v>0.3</v>
       </c>
-      <c r="I87" s="9">
+      <c r="I88" s="9">
         <v>10.8</v>
       </c>
-      <c r="J87" s="9">
+      <c r="J88" s="9">
         <v>0.5</v>
       </c>
-      <c r="K87" s="9">
+      <c r="K88" s="9">
         <v>0.53</v>
       </c>
-      <c r="L87" s="9">
+      <c r="L88" s="9">
         <v>0.04</v>
       </c>
-      <c r="M87" s="9">
+      <c r="M88" s="9">
         <v>256</v>
       </c>
-      <c r="N87" s="9">
+      <c r="N88" s="9">
         <v>5</v>
       </c>
-      <c r="O87" s="9">
+      <c r="O88" s="9">
         <v>51878.89</v>
       </c>
-      <c r="P87" s="9">
+      <c r="P88" s="9">
         <v>0.11</v>
       </c>
-      <c r="Q87" s="9">
+      <c r="Q88" s="9">
         <v>1.79</v>
       </c>
-      <c r="R87" s="9">
+      <c r="R88" s="9">
         <v>0.1</v>
       </c>
-      <c r="S87" s="9">
+      <c r="S88" s="9">
         <v>1.1299999999999999E-3</v>
       </c>
-      <c r="T87" s="9">
+      <c r="T88" s="9">
         <v>1.8000000000000001E-4</v>
       </c>
-      <c r="U87" s="9">
+      <c r="U88" s="9">
         <v>1.41</v>
       </c>
-      <c r="V87" s="9">
+      <c r="V88" s="9">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="C88">
+    <row r="89" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C89" s="13">
         <v>3002</v>
       </c>
-      <c r="D88">
+      <c r="D89" s="13">
         <v>17.697800000000001</v>
       </c>
-      <c r="E88">
+      <c r="E89" s="13">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F88">
+      <c r="F89" s="13">
         <v>414.5</v>
       </c>
-      <c r="G88">
+      <c r="G89" s="13">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H88">
+      <c r="H89" s="13">
         <v>0.3</v>
       </c>
-      <c r="I88">
+      <c r="I89" s="13">
         <v>42.7</v>
       </c>
-      <c r="J88">
+      <c r="J89" s="13">
         <v>0.5</v>
       </c>
-      <c r="K88">
+      <c r="K89" s="13">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="L88">
+      <c r="L89" s="13">
         <v>1.2E-2</v>
       </c>
-      <c r="M88">
+      <c r="M89" s="13">
         <v>130</v>
       </c>
-      <c r="N88">
+      <c r="N89" s="13">
         <v>30</v>
       </c>
-      <c r="O88">
+      <c r="O89" s="13">
         <v>48961.8</v>
       </c>
-      <c r="P88">
+      <c r="P89" s="13">
         <v>1.4</v>
       </c>
-      <c r="Q88">
+      <c r="Q89" s="13">
         <v>10.38</v>
       </c>
-      <c r="R88">
+      <c r="R89" s="13">
         <v>0.12</v>
       </c>
-      <c r="S88" s="1">
+      <c r="S89" s="13">
         <v>0.14199999999999999</v>
       </c>
-      <c r="T88" s="1">
+      <c r="T89" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="U88">
+      <c r="U89" s="13">
         <v>2.02</v>
       </c>
-      <c r="V88">
+      <c r="V89" s="13">
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C89" s="9">
+    <row r="90" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B90"/>
+      <c r="C90" s="9">
         <v>25004</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D90" s="9">
         <v>21.283999999999999</v>
       </c>
-      <c r="E89" s="9">
+      <c r="E90" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F89" s="9">
+      <c r="F90" s="9">
         <v>138.30000000000001</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G90" s="9">
         <v>1.2</v>
       </c>
-      <c r="H89" s="9">
+      <c r="H90" s="9">
         <v>0.3</v>
       </c>
-      <c r="I89" s="9">
+      <c r="I90" s="9">
         <v>17.53</v>
       </c>
-      <c r="J89" s="9">
+      <c r="J90" s="9">
         <v>0.23</v>
       </c>
-      <c r="K89" s="9">
+      <c r="K90" s="9">
         <v>0.41699999999999998</v>
       </c>
-      <c r="L89" s="9">
+      <c r="L90" s="9">
         <v>1.6E-2</v>
       </c>
-      <c r="M89" s="9">
+      <c r="M90" s="9">
         <v>297.39999999999998</v>
       </c>
-      <c r="N89" s="9">
+      <c r="N90" s="9">
         <v>2.1</v>
       </c>
-      <c r="O89" s="9">
+      <c r="O90" s="9">
         <v>52029.5</v>
       </c>
-      <c r="P89" s="9">
+      <c r="P90" s="9">
         <v>0.21</v>
       </c>
-      <c r="Q89" s="9">
+      <c r="Q90" s="9">
         <v>4.66</v>
       </c>
-      <c r="R89" s="9">
+      <c r="R90" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="S89" s="9">
+      <c r="S90" s="9">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="T89" s="9">
+      <c r="T90" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="U89" s="9">
+      <c r="U90" s="9">
         <v>0.48</v>
       </c>
-      <c r="V89" s="9">
+      <c r="V90" s="9">
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="C90">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A91" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C91">
         <v>59003</v>
       </c>
-      <c r="D90">
+      <c r="D91">
         <v>21.367999999999999</v>
       </c>
-      <c r="E90">
+      <c r="E91">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F90">
+      <c r="F91">
         <v>99.7</v>
       </c>
-      <c r="G90">
+      <c r="G91">
         <v>2.5</v>
       </c>
-      <c r="H90">
+      <c r="H91">
         <v>0.3</v>
       </c>
-      <c r="I90">
+      <c r="I91">
         <v>31.6</v>
       </c>
-      <c r="J90">
+      <c r="J91">
         <v>0.4</v>
       </c>
-      <c r="K90">
+      <c r="K91">
         <v>0.27500000000000002</v>
       </c>
-      <c r="L90">
+      <c r="L91">
         <v>1.6E-2</v>
       </c>
-      <c r="M90">
+      <c r="M91">
         <v>187.1</v>
       </c>
-      <c r="N90">
+      <c r="N91">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O90">
+      <c r="O91">
         <v>52336.13</v>
       </c>
-      <c r="P90">
+      <c r="P91">
         <v>0.16</v>
       </c>
-      <c r="Q90">
+      <c r="Q91">
         <v>8.93</v>
       </c>
-      <c r="R90">
+      <c r="R91">
         <v>0.11</v>
       </c>
-      <c r="S90" s="1">
+      <c r="S91" s="1">
         <v>6.2199999999999998E-2</v>
       </c>
-      <c r="T90" s="1">
+      <c r="T91" s="1">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="U90">
+      <c r="U91">
         <v>0.8</v>
       </c>
-      <c r="V90">
+      <c r="V91">
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C91" s="9">
+    <row r="92" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C92" s="9">
         <v>31004</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D92" s="9">
         <v>22.856999999999999</v>
       </c>
-      <c r="E91" s="9">
+      <c r="E92" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F91" s="9">
+      <c r="F92" s="9">
         <v>84.3</v>
       </c>
-      <c r="G91" s="9">
+      <c r="G92" s="9">
         <v>2.8</v>
       </c>
-      <c r="H91" s="9">
+      <c r="H92" s="9">
         <v>1.3</v>
       </c>
-      <c r="I91" s="9">
+      <c r="I92" s="9">
         <v>14</v>
       </c>
-      <c r="J91" s="9">
+      <c r="J92" s="9">
         <v>3</v>
       </c>
-      <c r="K91" s="9">
+      <c r="K92" s="9">
         <v>0.39</v>
       </c>
-      <c r="L91" s="9">
+      <c r="L92" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M91" s="9">
+      <c r="M92" s="9">
         <v>307</v>
       </c>
-      <c r="N91" s="9">
+      <c r="N92" s="9">
         <v>8</v>
       </c>
-      <c r="O91" s="9">
+      <c r="O92" s="9">
         <v>55742.2</v>
       </c>
-      <c r="P91" s="9">
+      <c r="P92" s="9">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q91" s="9">
+      <c r="Q92" s="9">
         <v>4</v>
       </c>
-      <c r="R91" s="9">
+      <c r="R92" s="9">
         <v>0.8</v>
       </c>
-      <c r="S91" s="9">
+      <c r="S92" s="9">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="T91" s="9">
+      <c r="T92" s="9">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="U91" s="9">
+      <c r="U92" s="9">
         <v>0.42</v>
       </c>
-      <c r="V91" s="9">
+      <c r="V92" s="9">
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C92" s="9">
+    <row r="93" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C93" s="9">
         <v>21007</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D93" s="9">
         <v>23.920999999999999</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E93" s="9">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="F92" s="9">
+      <c r="F93" s="9">
         <v>49.6</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G93" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H92" s="9">
+      <c r="H93" s="9">
         <v>0.5</v>
       </c>
-      <c r="I92" s="9">
+      <c r="I93" s="9">
         <v>16.2</v>
       </c>
-      <c r="J92" s="9">
+      <c r="J93" s="9">
         <v>0.4</v>
       </c>
-      <c r="K92" s="9">
+      <c r="K93" s="9">
         <v>0.4</v>
-      </c>
-      <c r="L92" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="M92" s="9">
-        <v>248</v>
-      </c>
-      <c r="N92" s="9">
-        <v>6</v>
-      </c>
-      <c r="O92" s="9">
-        <v>52123.3</v>
-      </c>
-      <c r="P92" s="9">
-        <v>0.4</v>
-      </c>
-      <c r="Q92" s="9">
-        <v>4.87</v>
-      </c>
-      <c r="R92" s="9">
-        <v>0.13</v>
-      </c>
-      <c r="S92" s="9">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="T92" s="9">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="U92" s="9">
-        <v>0.88</v>
-      </c>
-      <c r="V92" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="3:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="9">
-        <v>35020</v>
-      </c>
-      <c r="D93" s="9">
-        <v>24.736999999999998</v>
-      </c>
-      <c r="E93" s="9">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="F93" s="9">
-        <v>45.4</v>
-      </c>
-      <c r="G93" s="9">
-        <v>1.4</v>
-      </c>
-      <c r="H93" s="9">
-        <v>0.17</v>
-      </c>
-      <c r="I93" s="9">
-        <v>12.4</v>
-      </c>
-      <c r="J93" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="K93" s="9">
-        <v>0.36</v>
       </c>
       <c r="L93" s="9">
         <v>0.03</v>
       </c>
       <c r="M93" s="9">
-        <v>136</v>
+        <v>248</v>
       </c>
       <c r="N93" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O93" s="9">
-        <v>52042.16</v>
+        <v>52123.3</v>
       </c>
       <c r="P93" s="9">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="Q93" s="9">
-        <v>3.93</v>
+        <v>4.87</v>
       </c>
       <c r="R93" s="9">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="S93" s="9">
-        <v>4.0000000000000001E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="T93" s="9">
-        <v>4.0000000000000002E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="U93" s="9">
-        <v>0.57999999999999996</v>
+        <v>0.88</v>
       </c>
       <c r="V93" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="C94">
+    <row r="94" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C94" s="9">
+        <v>35020</v>
+      </c>
+      <c r="D94" s="9">
+        <v>24.736999999999998</v>
+      </c>
+      <c r="E94" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F94" s="9">
+        <v>45.4</v>
+      </c>
+      <c r="G94" s="9">
+        <v>1.4</v>
+      </c>
+      <c r="H94" s="9">
+        <v>0.17</v>
+      </c>
+      <c r="I94" s="9">
+        <v>12.4</v>
+      </c>
+      <c r="J94" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="K94" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="L94" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="M94" s="9">
+        <v>136</v>
+      </c>
+      <c r="N94" s="9">
+        <v>4</v>
+      </c>
+      <c r="O94" s="9">
+        <v>52042.16</v>
+      </c>
+      <c r="P94" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="Q94" s="9">
+        <v>3.93</v>
+      </c>
+      <c r="R94" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="S94" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T94" s="9">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="U94" s="9">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="V94" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="C95">
         <v>24012</v>
       </c>
-      <c r="D94">
+      <c r="D95">
         <v>25.526599999999998</v>
       </c>
-      <c r="E94">
+      <c r="E95">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="F94">
+      <c r="F95">
         <v>114.6</v>
       </c>
-      <c r="G94">
+      <c r="G95">
         <v>1.69</v>
       </c>
-      <c r="H94">
+      <c r="H95">
         <v>0.15</v>
       </c>
-      <c r="I94">
+      <c r="I95">
         <v>19.100000000000001</v>
       </c>
-      <c r="J94">
+      <c r="J95">
         <v>0.3</v>
       </c>
-      <c r="K94">
+      <c r="K95">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="L94">
+      <c r="L95">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="M94">
+      <c r="M95">
         <v>120</v>
       </c>
-      <c r="N94">
+      <c r="N95">
         <v>170</v>
       </c>
-      <c r="O94">
+      <c r="O95">
         <v>52137</v>
       </c>
-      <c r="P94">
+      <c r="P95">
         <v>12</v>
       </c>
-      <c r="Q94">
+      <c r="Q95">
         <v>6.69</v>
       </c>
-      <c r="R94">
+      <c r="R95">
         <v>0.09</v>
       </c>
-      <c r="S94" s="1">
+      <c r="S95" s="1">
         <v>1.83E-2</v>
       </c>
-      <c r="T94" s="1">
+      <c r="T95" s="1">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="U94">
+      <c r="U95">
         <v>0.53</v>
-      </c>
-      <c r="V94">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
-      <c r="C95">
-        <v>39013</v>
-      </c>
-      <c r="D95">
-        <v>36.707999999999998</v>
-      </c>
-      <c r="E95">
-        <v>0.01</v>
-      </c>
-      <c r="F95">
-        <v>99.2</v>
-      </c>
-      <c r="G95">
-        <v>2.7</v>
-      </c>
-      <c r="H95">
-        <v>0.6</v>
-      </c>
-      <c r="I95">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="J95">
-        <v>0.8</v>
-      </c>
-      <c r="K95">
-        <v>0.06</v>
-      </c>
-      <c r="L95">
-        <v>0.05</v>
-      </c>
-      <c r="M95">
-        <v>240</v>
-      </c>
-      <c r="N95">
-        <v>40</v>
-      </c>
-      <c r="O95">
-        <v>54427</v>
-      </c>
-      <c r="P95">
-        <v>4</v>
-      </c>
-      <c r="Q95">
-        <v>8.6</v>
-      </c>
-      <c r="R95">
-        <v>0.4</v>
-      </c>
-      <c r="S95" s="1">
-        <v>1.9E-2</v>
-      </c>
-      <c r="T95" s="1">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="U95">
-        <v>2</v>
       </c>
       <c r="V95">
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C96">
-        <v>8012</v>
+        <v>39013</v>
       </c>
       <c r="D96">
-        <v>40.744</v>
+        <v>36.707999999999998</v>
       </c>
       <c r="E96">
-        <v>8.0000000000000002E-3</v>
+        <v>0.01</v>
       </c>
       <c r="F96">
-        <v>50</v>
+        <v>99.2</v>
       </c>
       <c r="G96">
-        <v>1.21</v>
+        <v>2.7</v>
       </c>
       <c r="H96">
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="I96">
-        <v>14.21</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="J96">
-        <v>0.18</v>
+        <v>0.8</v>
       </c>
       <c r="K96">
-        <v>0.58599999999999997</v>
+        <v>0.06</v>
       </c>
       <c r="L96">
-        <v>8.9999999999999993E-3</v>
+        <v>0.05</v>
       </c>
       <c r="M96">
-        <v>213.9</v>
+        <v>240</v>
       </c>
       <c r="N96">
-        <v>1.4</v>
+        <v>40</v>
       </c>
       <c r="O96">
-        <v>52417.46</v>
+        <v>54427</v>
       </c>
       <c r="P96">
-        <v>0.13</v>
+        <v>4</v>
       </c>
       <c r="Q96">
-        <v>6.45</v>
+        <v>8.6</v>
       </c>
       <c r="R96">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="S96" s="1">
-        <v>6.4999999999999997E-3</v>
+        <v>1.9E-2</v>
       </c>
       <c r="T96" s="1">
-        <v>2.9999999999999997E-4</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U96">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="V96">
         <v>18</v>
@@ -2982,619 +3010,619 @@
     </row>
     <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97">
-        <v>53003</v>
+        <v>8012</v>
       </c>
       <c r="D97">
-        <v>42.54</v>
+        <v>40.744</v>
       </c>
       <c r="E97">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F97">
+        <v>50</v>
+      </c>
+      <c r="G97">
+        <v>1.21</v>
+      </c>
+      <c r="H97">
+        <v>0.12</v>
+      </c>
+      <c r="I97">
+        <v>14.21</v>
+      </c>
+      <c r="J97">
+        <v>0.18</v>
+      </c>
+      <c r="K97">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="L97">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="M97">
+        <v>213.9</v>
+      </c>
+      <c r="N97">
+        <v>1.4</v>
+      </c>
+      <c r="O97">
+        <v>52417.46</v>
+      </c>
+      <c r="P97">
+        <v>0.13</v>
+      </c>
+      <c r="Q97">
+        <v>6.45</v>
+      </c>
+      <c r="R97">
         <v>0.1</v>
       </c>
-      <c r="F97">
-        <v>23.7</v>
-      </c>
-      <c r="G97">
-        <v>1.9</v>
-      </c>
-      <c r="H97">
-        <v>0.5</v>
-      </c>
-      <c r="I97">
-        <v>5.4</v>
-      </c>
-      <c r="J97">
-        <v>1</v>
-      </c>
-      <c r="K97">
-        <v>0.39</v>
-      </c>
-      <c r="L97">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M97">
-        <v>77</v>
-      </c>
-      <c r="N97">
-        <v>14</v>
-      </c>
-      <c r="O97">
-        <v>55107.7</v>
-      </c>
-      <c r="P97">
-        <v>2</v>
-      </c>
-      <c r="Q97">
-        <v>2.9</v>
-      </c>
-      <c r="R97">
-        <v>0.6</v>
-      </c>
       <c r="S97" s="1">
-        <v>5.0000000000000001E-4</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="T97" s="1">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="U97">
-        <v>0.73</v>
+        <v>0.45</v>
       </c>
       <c r="V97">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98">
-        <v>26007</v>
+        <v>53003</v>
       </c>
       <c r="D98">
-        <v>46.692999999999998</v>
+        <v>42.54</v>
       </c>
       <c r="E98">
-        <v>7.0000000000000001E-3</v>
+        <v>0.1</v>
       </c>
       <c r="F98">
-        <v>87.7</v>
+        <v>23.7</v>
       </c>
       <c r="G98">
-        <v>2.91</v>
+        <v>1.9</v>
       </c>
       <c r="H98">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="I98">
-        <v>24.9</v>
+        <v>5.4</v>
       </c>
       <c r="J98">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="K98">
-        <v>0.27700000000000002</v>
+        <v>0.39</v>
       </c>
       <c r="L98">
-        <v>1.0999999999999999E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M98">
-        <v>297</v>
+        <v>77</v>
       </c>
       <c r="N98">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O98">
-        <v>53070.2</v>
+        <v>55107.7</v>
       </c>
       <c r="P98">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="Q98">
-        <v>15.35</v>
+        <v>2.9</v>
       </c>
       <c r="R98">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="S98" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="T98" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="U98">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="V98">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99">
-        <v>20010</v>
+        <v>26007</v>
       </c>
       <c r="D99">
-        <v>51</v>
+        <v>46.692999999999998</v>
       </c>
       <c r="E99">
-        <v>7.0000000000000007E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F99">
-        <v>33.1</v>
+        <v>87.7</v>
       </c>
       <c r="G99">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="H99">
+        <v>0.24</v>
+      </c>
+      <c r="I99">
+        <v>24.9</v>
+      </c>
+      <c r="J99">
+        <v>0.4</v>
+      </c>
+      <c r="K99">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="L99">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="M99">
+        <v>297</v>
+      </c>
+      <c r="N99">
+        <v>4</v>
+      </c>
+      <c r="O99">
+        <v>53070.2</v>
+      </c>
+      <c r="P99">
         <v>0.5</v>
       </c>
-      <c r="I99">
-        <v>15.8</v>
-      </c>
-      <c r="J99">
-        <v>2.4</v>
-      </c>
-      <c r="K99">
-        <v>0.53</v>
-      </c>
-      <c r="L99">
-        <v>0.06</v>
-      </c>
-      <c r="M99">
-        <v>135</v>
-      </c>
-      <c r="N99">
-        <v>9</v>
-      </c>
-      <c r="O99">
-        <v>53102.8</v>
-      </c>
-      <c r="P99">
-        <v>1.2</v>
-      </c>
       <c r="Q99">
-        <v>9.4</v>
+        <v>15.35</v>
       </c>
       <c r="R99">
-        <v>1.5</v>
+        <v>0.23</v>
       </c>
       <c r="S99" s="1">
-        <v>1.2999999999999999E-2</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="T99" s="1">
-        <v>6.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U99">
-        <v>1.5</v>
+        <v>0.74</v>
       </c>
       <c r="V99">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100">
-        <v>66016</v>
+        <v>20010</v>
       </c>
       <c r="D100">
-        <v>59.383000000000003</v>
+        <v>51</v>
       </c>
       <c r="E100">
-        <v>1.7999999999999999E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F100">
-        <v>49.9</v>
+        <v>33.1</v>
       </c>
       <c r="G100">
-        <v>2.2000000000000002</v>
+        <v>3.1</v>
       </c>
       <c r="H100">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I100">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="J100">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="K100">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="L100">
-        <v>2.3E-2</v>
+        <v>0.06</v>
       </c>
       <c r="M100">
-        <v>329</v>
+        <v>135</v>
       </c>
       <c r="N100">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O100">
-        <v>54456.9</v>
+        <v>53102.8</v>
       </c>
       <c r="P100">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="Q100">
-        <v>15.9</v>
+        <v>9.4</v>
       </c>
       <c r="R100">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="S100" s="1">
-        <v>4.5100000000000001E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="T100" s="1">
-        <v>2.2000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="U100">
-        <v>0.87</v>
+        <v>1.5</v>
       </c>
       <c r="V100">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101">
-        <v>34006</v>
+        <v>66016</v>
       </c>
       <c r="D101">
-        <v>60.48</v>
+        <v>59.383000000000003</v>
       </c>
       <c r="E101">
-        <v>0.04</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="F101">
-        <v>20.2</v>
+        <v>49.9</v>
       </c>
       <c r="G101">
-        <v>1.3</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H101">
         <v>0.3</v>
       </c>
       <c r="I101">
-        <v>14.2</v>
+        <v>19.8</v>
       </c>
       <c r="J101">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K101">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="L101">
-        <v>0.03</v>
+        <v>2.3E-2</v>
       </c>
       <c r="M101">
-        <v>226</v>
+        <v>329</v>
       </c>
       <c r="N101">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O101">
-        <v>55353.8</v>
+        <v>54456.9</v>
       </c>
       <c r="P101">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="Q101">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
       <c r="R101">
         <v>0.3</v>
       </c>
       <c r="S101" s="1">
-        <v>1.6299999999999999E-2</v>
+        <v>4.5100000000000001E-2</v>
       </c>
       <c r="T101" s="1">
-        <v>1.4E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="U101">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="V101">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102">
-        <v>8007</v>
+        <v>34006</v>
       </c>
       <c r="D102">
-        <v>66.837000000000003</v>
+        <v>60.48</v>
       </c>
       <c r="E102">
-        <v>1.6E-2</v>
+        <v>0.04</v>
       </c>
       <c r="F102">
-        <v>82.6</v>
+        <v>20.2</v>
       </c>
       <c r="G102">
-        <v>3.74</v>
+        <v>1.3</v>
       </c>
       <c r="H102">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I102">
-        <v>4.04</v>
+        <v>14.2</v>
       </c>
       <c r="J102">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="K102">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="L102">
         <v>0.03</v>
       </c>
       <c r="M102">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="N102">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O102">
-        <v>51623.199999999997</v>
+        <v>55353.8</v>
       </c>
       <c r="P102">
         <v>1.2</v>
       </c>
       <c r="Q102">
-        <v>3.62</v>
+        <v>11.4</v>
       </c>
       <c r="R102">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="S102" s="1">
-        <v>4.2000000000000002E-4</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="T102" s="1">
-        <v>4.0000000000000003E-5</v>
+        <v>1.4E-3</v>
       </c>
       <c r="U102">
-        <v>0.21</v>
+        <v>0.89</v>
       </c>
       <c r="V102">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C103">
-        <v>36043</v>
+        <v>8007</v>
       </c>
       <c r="D103">
-        <v>71.7</v>
+        <v>66.837000000000003</v>
       </c>
       <c r="E103">
-        <v>0.04</v>
+        <v>1.6E-2</v>
       </c>
       <c r="F103">
-        <v>13.3</v>
+        <v>82.6</v>
       </c>
       <c r="G103">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="H103">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I103">
-        <v>14.2</v>
+        <v>4.04</v>
       </c>
       <c r="J103">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="K103">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="L103">
         <v>0.03</v>
       </c>
       <c r="M103">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="N103">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O103">
-        <v>56244</v>
+        <v>51623.199999999997</v>
       </c>
       <c r="P103">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="Q103">
-        <v>13.97</v>
+        <v>3.62</v>
       </c>
       <c r="R103">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="S103" s="1">
-        <v>2.1100000000000001E-2</v>
+        <v>4.2000000000000002E-4</v>
       </c>
       <c r="T103" s="1">
-        <v>1.1000000000000001E-3</v>
+        <v>4.0000000000000003E-5</v>
       </c>
       <c r="U103">
-        <v>0.47</v>
+        <v>0.21</v>
       </c>
       <c r="V103">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C104">
-        <v>54027</v>
+        <v>36043</v>
       </c>
       <c r="D104">
-        <v>73.027000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="E104">
-        <v>1.9E-2</v>
+        <v>0.04</v>
       </c>
       <c r="F104">
-        <v>31.1</v>
+        <v>13.3</v>
       </c>
       <c r="G104">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="H104">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="I104">
-        <v>21.2</v>
+        <v>14.2</v>
       </c>
       <c r="J104">
         <v>0.3</v>
       </c>
       <c r="K104">
-        <v>0.55000000000000004</v>
+        <v>0.09</v>
       </c>
       <c r="L104">
         <v>0.03</v>
       </c>
       <c r="M104">
-        <v>41.3</v>
+        <v>348</v>
       </c>
       <c r="N104">
-        <v>2.2000000000000002</v>
+        <v>15</v>
       </c>
       <c r="O104">
-        <v>55589.2</v>
+        <v>56244</v>
       </c>
       <c r="P104">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="Q104">
-        <v>17.899999999999999</v>
+        <v>13.97</v>
       </c>
       <c r="R104">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="S104" s="1">
-        <v>4.2500000000000003E-2</v>
+        <v>2.1100000000000001E-2</v>
       </c>
       <c r="T104" s="1">
-        <v>2.2000000000000001E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="U104">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="V104">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C105">
-        <v>22020</v>
+        <v>54027</v>
       </c>
       <c r="D105">
-        <v>81.680000000000007</v>
+        <v>73.027000000000001</v>
       </c>
       <c r="E105">
-        <v>0.13</v>
+        <v>1.9E-2</v>
       </c>
       <c r="F105">
-        <v>13.7</v>
+        <v>31.1</v>
       </c>
       <c r="G105">
-        <v>0.46</v>
+        <v>3.09</v>
       </c>
       <c r="H105">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I105">
-        <v>10.199999999999999</v>
+        <v>21.2</v>
       </c>
       <c r="J105">
         <v>0.3</v>
       </c>
       <c r="K105">
-        <v>0.14000000000000001</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L105">
         <v>0.03</v>
       </c>
       <c r="M105">
-        <v>352</v>
+        <v>41.3</v>
       </c>
       <c r="N105">
-        <v>14</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="O105">
-        <v>52125</v>
+        <v>55589.2</v>
       </c>
       <c r="P105">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="Q105">
-        <v>11.4</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="R105">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="S105" s="1">
-        <v>8.8000000000000005E-3</v>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="T105" s="1">
-        <v>8.0000000000000004E-4</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="U105">
-        <v>0.69</v>
+        <v>0.49</v>
       </c>
       <c r="V105">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C106">
-        <v>24004</v>
+        <v>22020</v>
       </c>
       <c r="D106">
-        <v>83.33</v>
+        <v>81.680000000000007</v>
       </c>
       <c r="E106">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="F106">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="G106">
-        <v>1.08</v>
+        <v>0.46</v>
       </c>
       <c r="H106">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I106">
-        <v>20.399999999999999</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J106">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K106">
-        <v>0.501</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L106">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="M106">
-        <v>172</v>
+        <v>352</v>
       </c>
       <c r="N106">
+        <v>14</v>
+      </c>
+      <c r="O106">
+        <v>52125</v>
+      </c>
+      <c r="P106">
         <v>3</v>
       </c>
-      <c r="O106">
-        <v>55281.1</v>
-      </c>
-      <c r="P106">
-        <v>0.5</v>
-      </c>
       <c r="Q106">
-        <v>20.2</v>
+        <v>11.4</v>
       </c>
       <c r="R106">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="S106" s="1">
-        <v>4.8000000000000001E-2</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="T106" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="U106">
-        <v>0.62</v>
+        <v>0.69</v>
       </c>
       <c r="V106">
         <v>12</v>
@@ -3602,929 +3630,929 @@
     </row>
     <row r="107" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C107">
-        <v>24031</v>
+        <v>24004</v>
       </c>
       <c r="D107">
-        <v>91.2</v>
+        <v>83.33</v>
       </c>
       <c r="E107">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="F107">
-        <v>16.2</v>
+        <v>13.2</v>
       </c>
       <c r="G107">
-        <v>2.15</v>
+        <v>1.08</v>
       </c>
       <c r="H107">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="I107">
-        <v>16.899999999999999</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="J107">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K107">
-        <v>0.32300000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="L107">
-        <v>1.6E-2</v>
+        <v>0.01</v>
       </c>
       <c r="M107">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="N107">
         <v>3</v>
       </c>
       <c r="O107">
-        <v>54884</v>
+        <v>55281.1</v>
       </c>
       <c r="P107">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q107">
-        <v>20.100000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="R107">
         <v>0.4</v>
       </c>
       <c r="S107" s="1">
-        <v>3.9E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="T107" s="1">
-        <v>2.3999999999999998E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U107">
-        <v>0.69</v>
+        <v>0.62</v>
       </c>
       <c r="V107">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C108">
-        <v>30008</v>
+        <v>24031</v>
       </c>
       <c r="D108">
-        <v>93.16</v>
+        <v>91.2</v>
       </c>
       <c r="E108">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="F108">
-        <v>41.8</v>
+        <v>16.2</v>
       </c>
       <c r="G108">
-        <v>1.1399999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="H108">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="I108">
-        <v>4.43</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="J108">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="K108">
-        <v>0.46</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="L108">
-        <v>0.04</v>
+        <v>1.6E-2</v>
       </c>
       <c r="M108">
-        <v>297</v>
+        <v>14</v>
       </c>
       <c r="N108">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O108">
-        <v>55174</v>
+        <v>54884</v>
       </c>
       <c r="P108">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="Q108">
-        <v>5</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="R108">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="S108" s="1">
-        <v>5.9000000000000003E-4</v>
+        <v>3.9E-2</v>
       </c>
       <c r="T108" s="1">
-        <v>1E-4</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="U108">
-        <v>0.44</v>
+        <v>0.69</v>
       </c>
       <c r="V108">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C109">
-        <v>6004</v>
+        <v>30008</v>
       </c>
       <c r="D109">
-        <v>113.61499999999999</v>
+        <v>93.16</v>
       </c>
       <c r="E109">
-        <v>2.1999999999999999E-2</v>
+        <v>0.13</v>
       </c>
       <c r="F109">
-        <v>35.799999999999997</v>
+        <v>41.8</v>
       </c>
       <c r="G109">
-        <v>1.36</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="H109">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="I109">
-        <v>17.2</v>
+        <v>4.43</v>
       </c>
       <c r="J109">
+        <v>0.23</v>
+      </c>
+      <c r="K109">
+        <v>0.46</v>
+      </c>
+      <c r="L109">
+        <v>0.04</v>
+      </c>
+      <c r="M109">
+        <v>297</v>
+      </c>
+      <c r="N109">
+        <v>8</v>
+      </c>
+      <c r="O109">
+        <v>55174</v>
+      </c>
+      <c r="P109">
+        <v>3</v>
+      </c>
+      <c r="Q109">
+        <v>5</v>
+      </c>
+      <c r="R109">
         <v>0.3</v>
       </c>
-      <c r="K109">
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="L109">
-        <v>1.9E-2</v>
-      </c>
-      <c r="M109">
-        <v>166</v>
-      </c>
-      <c r="N109">
-        <v>6</v>
-      </c>
-      <c r="O109">
-        <v>49453.3</v>
-      </c>
-      <c r="P109">
-        <v>1.9</v>
-      </c>
-      <c r="Q109">
-        <v>26.5</v>
-      </c>
-      <c r="R109">
-        <v>0.4</v>
-      </c>
       <c r="S109" s="1">
-        <v>5.8000000000000003E-2</v>
+        <v>5.9000000000000003E-4</v>
       </c>
       <c r="T109" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="U109">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="V109">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C110">
-        <v>20013</v>
+        <v>6004</v>
       </c>
       <c r="D110">
-        <v>121.57</v>
+        <v>113.61499999999999</v>
       </c>
       <c r="E110">
-        <v>1.7000000000000001E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="F110">
-        <v>15.1</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="G110">
-        <v>2.23</v>
+        <v>1.36</v>
       </c>
       <c r="H110">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I110">
-        <v>15.6</v>
+        <v>17.2</v>
       </c>
       <c r="J110">
         <v>0.3</v>
       </c>
       <c r="K110">
-        <v>0.45400000000000001</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="L110">
-        <v>8.0000000000000002E-3</v>
+        <v>1.9E-2</v>
       </c>
       <c r="M110">
-        <v>255</v>
+        <v>166</v>
       </c>
       <c r="N110">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O110">
-        <v>52296.6</v>
+        <v>49453.3</v>
       </c>
       <c r="P110">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q110">
-        <v>23.2</v>
+        <v>26.5</v>
       </c>
       <c r="R110">
         <v>0.4</v>
       </c>
       <c r="S110" s="1">
-        <v>3.3599999999999998E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="T110" s="1">
-        <v>1.6999999999999999E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U110">
-        <v>0.26</v>
+        <v>0.89</v>
       </c>
       <c r="V110">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C111">
-        <v>17025</v>
+        <v>20013</v>
       </c>
       <c r="D111">
-        <v>135</v>
+        <v>121.57</v>
       </c>
       <c r="E111">
-        <v>0.3</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="F111">
-        <v>8.8000000000000007</v>
+        <v>15.1</v>
       </c>
       <c r="G111">
-        <v>0.7</v>
+        <v>2.23</v>
       </c>
       <c r="H111">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I111">
-        <v>10.3</v>
+        <v>15.6</v>
       </c>
       <c r="J111">
         <v>0.3</v>
       </c>
       <c r="K111">
-        <v>0.28000000000000003</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="L111">
-        <v>0.03</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="M111">
-        <v>300</v>
+        <v>255</v>
       </c>
       <c r="N111">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O111">
-        <v>52094</v>
+        <v>52296.6</v>
       </c>
       <c r="P111">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="Q111">
-        <v>18.3</v>
+        <v>23.2</v>
       </c>
       <c r="R111">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="S111" s="1">
-        <v>1.35E-2</v>
+        <v>3.3599999999999998E-2</v>
       </c>
       <c r="T111" s="1">
-        <v>1.1999999999999999E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="U111">
-        <v>0.68</v>
+        <v>0.26</v>
       </c>
       <c r="V111">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="112" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C112">
-        <v>20002</v>
+        <v>17025</v>
       </c>
       <c r="D112">
-        <v>141.74</v>
+        <v>135</v>
       </c>
       <c r="E112">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F112">
-        <v>30.4</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="G112">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="H112">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I112">
-        <v>7.1</v>
+        <v>10.3</v>
       </c>
       <c r="J112">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="K112">
-        <v>0.52</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="L112">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="M112">
-        <v>197</v>
+        <v>300</v>
       </c>
       <c r="N112">
         <v>8</v>
       </c>
       <c r="O112">
-        <v>52665</v>
+        <v>52094</v>
       </c>
       <c r="P112">
         <v>4</v>
       </c>
       <c r="Q112">
-        <v>11.8</v>
+        <v>18.3</v>
       </c>
       <c r="R112">
-        <v>2.2999999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="S112" s="1">
-        <v>3.3E-3</v>
+        <v>1.35E-2</v>
       </c>
       <c r="T112" s="1">
-        <v>1.9E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="U112">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="V112">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C113">
-        <v>18019</v>
+        <v>20002</v>
       </c>
       <c r="D113">
-        <v>142.30000000000001</v>
+        <v>141.74</v>
       </c>
       <c r="E113">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="F113">
-        <v>13.3</v>
+        <v>30.4</v>
       </c>
       <c r="G113">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="H113">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="I113">
-        <v>4.78</v>
+        <v>7.1</v>
       </c>
       <c r="J113">
-        <v>0.17</v>
+        <v>1.3</v>
       </c>
       <c r="K113">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="L113">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="M113">
-        <v>304</v>
+        <v>197</v>
       </c>
       <c r="N113">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O113">
-        <v>52045.1</v>
+        <v>52665</v>
       </c>
       <c r="P113">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="Q113">
-        <v>8.9</v>
+        <v>11.8</v>
       </c>
       <c r="R113">
-        <v>0.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="S113" s="1">
-        <v>1.3799999999999999E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="T113" s="1">
-        <v>1.4999999999999999E-4</v>
+        <v>1.9E-3</v>
       </c>
       <c r="U113">
-        <v>0.34</v>
+        <v>1</v>
       </c>
       <c r="V113">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C114">
-        <v>14009</v>
+        <v>18019</v>
       </c>
       <c r="D114">
-        <v>174.464</v>
+        <v>142.30000000000001</v>
       </c>
       <c r="E114">
-        <v>0.02</v>
+        <v>0.3</v>
       </c>
       <c r="F114">
-        <v>23.4</v>
+        <v>13.3</v>
       </c>
       <c r="G114">
-        <v>2.63</v>
+        <v>1.84</v>
       </c>
       <c r="H114">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="I114">
-        <v>15.7</v>
+        <v>4.78</v>
       </c>
       <c r="J114">
-        <v>0.8</v>
+        <v>0.17</v>
       </c>
       <c r="K114">
-        <v>0.69099999999999995</v>
+        <v>0.32</v>
       </c>
       <c r="L114">
-        <v>1.7000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="M114">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="N114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O114">
-        <v>53620.3</v>
+        <v>52045.1</v>
       </c>
       <c r="P114">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q114">
-        <v>27.2</v>
+        <v>8.9</v>
       </c>
       <c r="R114">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="S114" s="1">
-        <v>2.5999999999999999E-2</v>
+        <v>1.3799999999999999E-3</v>
       </c>
       <c r="T114" s="1">
-        <v>4.0000000000000001E-3</v>
+        <v>1.4999999999999999E-4</v>
       </c>
       <c r="U114">
-        <v>0.72</v>
+        <v>0.34</v>
       </c>
       <c r="V114">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C115">
-        <v>36012</v>
+        <v>14009</v>
       </c>
       <c r="D115">
-        <v>176.4</v>
+        <v>174.464</v>
       </c>
       <c r="E115">
-        <v>0.6</v>
+        <v>0.02</v>
       </c>
       <c r="F115">
-        <v>20.6</v>
+        <v>23.4</v>
       </c>
       <c r="G115">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="H115">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="I115">
-        <v>5.8</v>
+        <v>15.7</v>
       </c>
       <c r="J115">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K115">
-        <v>0.65</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="L115">
-        <v>0.04</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="M115">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="N115">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O115">
-        <v>54410</v>
+        <v>53620.3</v>
       </c>
       <c r="P115">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="Q115">
-        <v>10.6</v>
+        <v>27.2</v>
       </c>
       <c r="R115">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S115" s="1">
-        <v>1.5E-3</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="T115" s="1">
-        <v>5.9999999999999995E-4</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="U115">
-        <v>0.69</v>
+        <v>0.72</v>
       </c>
       <c r="V115">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C116">
-        <v>16011</v>
+        <v>36012</v>
       </c>
       <c r="D116">
-        <v>209.446</v>
+        <v>176.4</v>
       </c>
       <c r="E116">
-        <v>1.9E-2</v>
+        <v>0.6</v>
       </c>
       <c r="F116">
-        <v>6.9</v>
+        <v>20.6</v>
       </c>
       <c r="G116">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H116">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I116">
-        <v>18</v>
+        <v>5.8</v>
       </c>
       <c r="J116">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="K116">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="L116">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M116">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="N116">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="O116">
-        <v>55232</v>
+        <v>54410</v>
       </c>
       <c r="P116">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="Q116">
-        <v>20</v>
+        <v>10.6</v>
       </c>
       <c r="R116">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="S116" s="1">
-        <v>7.7000000000000002E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="T116" s="1">
-        <v>1.4E-2</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="U116">
-        <v>0.26</v>
+        <v>0.69</v>
       </c>
       <c r="V116">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C117">
-        <v>7009</v>
+        <v>16011</v>
       </c>
       <c r="D117">
-        <v>209.89</v>
+        <v>209.446</v>
       </c>
       <c r="E117">
-        <v>0.04</v>
+        <v>1.9E-2</v>
       </c>
       <c r="F117">
-        <v>23.1</v>
+        <v>6.9</v>
       </c>
       <c r="G117">
-        <v>0.22</v>
+        <v>3.1</v>
       </c>
       <c r="H117">
-        <v>0.11</v>
+        <v>0.5</v>
       </c>
       <c r="I117">
-        <v>20.5</v>
+        <v>18</v>
       </c>
       <c r="J117">
-        <v>0.3</v>
+        <v>10</v>
       </c>
       <c r="K117">
-        <v>0.58499999999999996</v>
+        <v>0.92</v>
       </c>
       <c r="L117">
-        <v>7.0000000000000001E-3</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M117">
-        <v>216.5</v>
+        <v>273</v>
       </c>
       <c r="N117">
-        <v>1.1000000000000001</v>
+        <v>21</v>
       </c>
       <c r="O117">
-        <v>49988.9</v>
+        <v>55232</v>
       </c>
       <c r="P117">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q117">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="R117">
-        <v>0.8</v>
+        <v>14</v>
       </c>
       <c r="S117" s="1">
-        <v>0.1</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="T117" s="1">
-        <v>5.0000000000000001E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="U117">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="V117">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C118">
-        <v>52015</v>
+        <v>7009</v>
       </c>
       <c r="D118">
-        <v>247.34</v>
+        <v>209.89</v>
       </c>
       <c r="E118">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="F118">
-        <v>12.2</v>
+        <v>23.1</v>
       </c>
       <c r="G118">
-        <v>1.36</v>
+        <v>0.22</v>
       </c>
       <c r="H118">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="I118">
-        <v>14.03</v>
+        <v>20.5</v>
       </c>
       <c r="J118">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="K118">
-        <v>5.2999999999999999E-2</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="L118">
-        <v>1.7999999999999999E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="M118">
-        <v>326</v>
+        <v>216.5</v>
       </c>
       <c r="N118">
-        <v>21</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O118">
-        <v>53291</v>
+        <v>49988.9</v>
       </c>
       <c r="P118">
-        <v>15</v>
+        <v>0.6</v>
       </c>
       <c r="Q118">
-        <v>47.6</v>
+        <v>48</v>
       </c>
       <c r="R118">
         <v>0.8</v>
       </c>
       <c r="S118" s="1">
-        <v>7.0999999999999994E-2</v>
+        <v>0.1</v>
       </c>
       <c r="T118" s="1">
-        <v>4.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="U118">
-        <v>0.69</v>
+        <v>0.61</v>
       </c>
       <c r="V118">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C119">
-        <v>37028</v>
+        <v>52015</v>
       </c>
       <c r="D119">
-        <v>288.5</v>
+        <v>247.34</v>
       </c>
       <c r="E119">
-        <v>1.7</v>
+        <v>0.18</v>
       </c>
       <c r="F119">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="G119">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="H119">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="I119">
-        <v>4.05</v>
+        <v>14.03</v>
       </c>
       <c r="J119">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="K119">
-        <v>0.31</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="L119">
-        <v>0.06</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="M119">
-        <v>250</v>
+        <v>326</v>
       </c>
       <c r="N119">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="O119">
-        <v>54638</v>
+        <v>53291</v>
       </c>
       <c r="P119">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q119">
-        <v>15.3</v>
+        <v>47.6</v>
       </c>
       <c r="R119">
         <v>0.8</v>
       </c>
       <c r="S119" s="1">
-        <v>1.6999999999999999E-3</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="T119" s="1">
-        <v>2.9999999999999997E-4</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="U119">
-        <v>0.56000000000000005</v>
+        <v>0.69</v>
       </c>
       <c r="V119">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C120">
-        <v>6001</v>
+        <v>37028</v>
       </c>
       <c r="D120">
-        <v>323.10000000000002</v>
+        <v>288.5</v>
       </c>
       <c r="E120">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="F120">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="G120">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="H120">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="I120">
-        <v>7</v>
+        <v>4.05</v>
       </c>
       <c r="J120">
-        <v>0.7</v>
+        <v>0.21</v>
       </c>
       <c r="K120">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="L120">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="M120">
-        <v>319</v>
+        <v>250</v>
       </c>
       <c r="N120">
+        <v>12</v>
+      </c>
+      <c r="O120">
+        <v>54638</v>
+      </c>
+      <c r="P120">
         <v>9</v>
       </c>
-      <c r="O120">
-        <v>55442</v>
-      </c>
-      <c r="P120">
-        <v>7</v>
-      </c>
       <c r="Q120">
-        <v>28</v>
+        <v>15.3</v>
       </c>
       <c r="R120">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="S120" s="1">
-        <v>8.9999999999999993E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="T120" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="U120">
-        <v>0.79</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="V120">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C121">
-        <v>29021</v>
+        <v>6001</v>
       </c>
       <c r="D121">
-        <v>370.3</v>
+        <v>323.10000000000002</v>
       </c>
       <c r="E121">
         <v>2.1</v>
       </c>
       <c r="F121">
-        <v>4.5999999999999996</v>
+        <v>6</v>
       </c>
       <c r="G121">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H121">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I121">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="J121">
         <v>0.7</v>
       </c>
       <c r="K121">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
       <c r="L121">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M121">
-        <v>118</v>
+        <v>319</v>
       </c>
       <c r="N121">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O121">
-        <v>54967</v>
+        <v>55442</v>
       </c>
       <c r="P121">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q121">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="R121">
         <v>3</v>
       </c>
       <c r="S121" s="1">
-        <v>7.9000000000000001E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="T121" s="1">
-        <v>1.2999999999999999E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U121">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="V121">
         <v>16</v>
@@ -4532,619 +4560,619 @@
     </row>
     <row r="122" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C122">
-        <v>40017</v>
+        <v>29021</v>
       </c>
       <c r="D122">
-        <v>370.5</v>
+        <v>370.3</v>
       </c>
       <c r="E122">
+        <v>2.1</v>
+      </c>
+      <c r="F122">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G122">
+        <v>1.2</v>
+      </c>
+      <c r="H122">
+        <v>0.4</v>
+      </c>
+      <c r="I122">
+        <v>12.8</v>
+      </c>
+      <c r="J122">
         <v>0.7</v>
       </c>
-      <c r="F122">
-        <v>11.7</v>
-      </c>
-      <c r="G122">
-        <v>2.5</v>
-      </c>
-      <c r="H122">
-        <v>0.3</v>
-      </c>
-      <c r="I122">
-        <v>6.1</v>
-      </c>
-      <c r="J122">
-        <v>0.4</v>
-      </c>
       <c r="K122">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="L122">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="M122">
-        <v>332</v>
+        <v>118</v>
       </c>
       <c r="N122">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O122">
-        <v>53502</v>
+        <v>54967</v>
       </c>
       <c r="P122">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q122">
-        <v>30.5</v>
+        <v>65</v>
       </c>
       <c r="R122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S122" s="1">
-        <v>8.3000000000000001E-3</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="T122" s="1">
-        <v>1.6000000000000001E-3</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="U122">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="V122">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C123">
-        <v>28004</v>
+        <v>40017</v>
       </c>
       <c r="D123">
-        <v>414</v>
+        <v>370.5</v>
       </c>
       <c r="E123">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="F123">
-        <v>3.7</v>
+        <v>11.7</v>
       </c>
       <c r="G123">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="H123">
+        <v>0.3</v>
+      </c>
+      <c r="I123">
+        <v>6.1</v>
+      </c>
+      <c r="J123">
         <v>0.4</v>
       </c>
-      <c r="I123">
-        <v>13</v>
-      </c>
-      <c r="J123">
-        <v>1.8</v>
-      </c>
       <c r="K123">
-        <v>0.71</v>
+        <v>0.16</v>
       </c>
       <c r="L123">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="M123">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="O123">
-        <v>55639</v>
+        <v>53502</v>
       </c>
       <c r="P123">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q123">
-        <v>52</v>
+        <v>30.5</v>
       </c>
       <c r="R123">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S123" s="1">
-        <v>3.4000000000000002E-2</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="T123" s="1">
-        <v>1.4999999999999999E-2</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="U123">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="V123">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="124" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C124">
-        <v>9001</v>
+        <v>28004</v>
       </c>
       <c r="D124">
-        <v>458.4</v>
+        <v>414</v>
       </c>
       <c r="E124">
-        <v>1.1000000000000001</v>
+        <v>3</v>
       </c>
       <c r="F124">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="G124">
-        <v>1.58</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H124">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I124">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J124">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="K124">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="L124">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="M124">
-        <v>249</v>
+        <v>119</v>
       </c>
       <c r="N124">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O124">
-        <v>55368</v>
+        <v>55639</v>
       </c>
       <c r="P124">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q124">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="R124">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S124" s="1">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="T124" s="1">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="T124" s="1">
-        <v>3.0000000000000001E-3</v>
-      </c>
       <c r="U124">
-        <v>0.56999999999999995</v>
+        <v>0.61</v>
       </c>
       <c r="V124">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C125">
-        <v>13007</v>
+        <v>9001</v>
       </c>
       <c r="D125">
-        <v>511</v>
+        <v>458.4</v>
       </c>
       <c r="E125">
-        <v>3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F125">
-        <v>5.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G125">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="H125">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="I125">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J125">
         <v>0.4</v>
       </c>
       <c r="K125">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="L125">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="M125">
-        <v>353</v>
+        <v>249</v>
       </c>
       <c r="N125">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O125">
-        <v>52927</v>
+        <v>55368</v>
       </c>
       <c r="P125">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Q125">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="R125">
         <v>3</v>
       </c>
       <c r="S125" s="1">
-        <v>1.7000000000000001E-4</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="T125" s="1">
-        <v>1.2E-4</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U125">
-        <v>0.45</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="V125">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C126">
-        <v>17005</v>
+        <v>13007</v>
       </c>
       <c r="D126">
-        <v>543.1</v>
+        <v>511</v>
       </c>
       <c r="E126">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F126">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="G126">
-        <v>1.08</v>
+        <v>1.92</v>
       </c>
       <c r="H126">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I126">
-        <v>9.83</v>
+        <v>1.7</v>
       </c>
       <c r="J126">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="K126">
-        <v>0.498</v>
+        <v>0.47</v>
       </c>
       <c r="L126">
-        <v>1.4999999999999999E-2</v>
+        <v>0.12</v>
       </c>
       <c r="M126">
-        <v>249.3</v>
+        <v>353</v>
       </c>
       <c r="N126">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="O126">
-        <v>52892</v>
+        <v>52927</v>
       </c>
       <c r="P126">
+        <v>20</v>
+      </c>
+      <c r="Q126">
+        <v>10</v>
+      </c>
+      <c r="R126">
         <v>3</v>
       </c>
-      <c r="Q126">
-        <v>63.7</v>
-      </c>
-      <c r="R126">
-        <v>1.3</v>
-      </c>
       <c r="S126" s="1">
-        <v>3.49E-2</v>
+        <v>1.7000000000000001E-4</v>
       </c>
       <c r="T126" s="1">
-        <v>1.9E-3</v>
+        <v>1.2E-4</v>
       </c>
       <c r="U126">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="V126">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C127">
-        <v>27020</v>
+        <v>17005</v>
       </c>
       <c r="D127">
-        <v>583</v>
+        <v>543.1</v>
       </c>
       <c r="E127">
+        <v>0.7</v>
+      </c>
+      <c r="F127">
+        <v>6.7</v>
+      </c>
+      <c r="G127">
+        <v>1.08</v>
+      </c>
+      <c r="H127">
+        <v>0.11</v>
+      </c>
+      <c r="I127">
+        <v>9.83</v>
+      </c>
+      <c r="J127">
+        <v>0.17</v>
+      </c>
+      <c r="K127">
+        <v>0.498</v>
+      </c>
+      <c r="L127">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M127">
+        <v>249.3</v>
+      </c>
+      <c r="N127">
+        <v>1.5</v>
+      </c>
+      <c r="O127">
+        <v>52892</v>
+      </c>
+      <c r="P127">
         <v>3</v>
       </c>
-      <c r="F127">
-        <v>4.2</v>
-      </c>
-      <c r="G127">
-        <v>2.44</v>
-      </c>
-      <c r="H127">
-        <v>0.15</v>
-      </c>
-      <c r="I127">
-        <v>5.3</v>
-      </c>
-      <c r="J127">
-        <v>0.3</v>
-      </c>
-      <c r="K127">
-        <v>0.26</v>
-      </c>
-      <c r="L127">
-        <v>0.05</v>
-      </c>
-      <c r="M127">
-        <v>268</v>
-      </c>
-      <c r="N127">
-        <v>9</v>
-      </c>
-      <c r="O127">
-        <v>52267</v>
-      </c>
-      <c r="P127">
-        <v>13</v>
-      </c>
       <c r="Q127">
-        <v>41.1</v>
+        <v>63.7</v>
       </c>
       <c r="R127">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="S127" s="1">
-        <v>8.2000000000000007E-3</v>
+        <v>3.49E-2</v>
       </c>
       <c r="T127" s="1">
-        <v>1.1999999999999999E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="U127">
-        <v>0.52</v>
+        <v>0.33</v>
       </c>
       <c r="V127">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C128">
-        <v>16006</v>
+        <v>27020</v>
       </c>
       <c r="D128">
-        <v>620.5</v>
+        <v>583</v>
       </c>
       <c r="E128">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="F128">
-        <v>8.8000000000000007</v>
+        <v>4.2</v>
       </c>
       <c r="G128">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="H128">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="I128">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="J128">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K128">
-        <v>0.71399999999999997</v>
+        <v>0.26</v>
       </c>
       <c r="L128">
-        <v>1.9E-2</v>
+        <v>0.05</v>
       </c>
       <c r="M128">
-        <v>211.9</v>
+        <v>268</v>
       </c>
       <c r="N128">
-        <v>2.2000000000000002</v>
+        <v>9</v>
       </c>
       <c r="O128">
-        <v>53378.9</v>
+        <v>52267</v>
       </c>
       <c r="P128">
-        <v>2.2999999999999998</v>
+        <v>13</v>
       </c>
       <c r="Q128">
-        <v>63</v>
+        <v>41.1</v>
       </c>
       <c r="R128">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="S128" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="T128" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="U128">
-        <v>0.77</v>
+        <v>0.52</v>
       </c>
       <c r="V128">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C129">
-        <v>69005</v>
+        <v>16006</v>
       </c>
       <c r="D129">
-        <v>640</v>
+        <v>620.5</v>
       </c>
       <c r="E129">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="F129">
-        <v>4.9000000000000004</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="G129">
-        <v>3.9</v>
+        <v>2.12</v>
       </c>
       <c r="H129">
-        <v>0.9</v>
+        <v>0.17</v>
       </c>
       <c r="I129">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="J129">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="K129">
-        <v>0.64</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="L129">
-        <v>0.09</v>
+        <v>1.9E-2</v>
       </c>
       <c r="M129">
-        <v>15</v>
+        <v>211.9</v>
       </c>
       <c r="N129">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O129">
+        <v>53378.9</v>
+      </c>
+      <c r="P129">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Q129">
+        <v>63</v>
+      </c>
+      <c r="R129">
         <v>3</v>
       </c>
-      <c r="O129">
-        <v>54836</v>
-      </c>
-      <c r="P129">
-        <v>4</v>
-      </c>
-      <c r="Q129">
-        <v>100</v>
-      </c>
-      <c r="R129">
-        <v>40</v>
-      </c>
       <c r="S129" s="1">
-        <v>0.11</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="T129" s="1">
-        <v>0.12</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U129">
         <v>0.77</v>
       </c>
       <c r="V129">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="130" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C130">
-        <v>49004</v>
+        <v>69005</v>
       </c>
       <c r="D130">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E130">
+        <v>5</v>
+      </c>
+      <c r="F130">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G130">
+        <v>3.9</v>
+      </c>
+      <c r="H130">
+        <v>0.9</v>
+      </c>
+      <c r="I130">
+        <v>15</v>
+      </c>
+      <c r="J130">
+        <v>6</v>
+      </c>
+      <c r="K130">
+        <v>0.64</v>
+      </c>
+      <c r="L130">
+        <v>0.09</v>
+      </c>
+      <c r="M130">
+        <v>15</v>
+      </c>
+      <c r="N130">
         <v>3</v>
       </c>
-      <c r="F130">
-        <v>7.9</v>
-      </c>
-      <c r="G130">
-        <v>0.5</v>
-      </c>
-      <c r="H130">
-        <v>1</v>
-      </c>
-      <c r="I130">
-        <v>16</v>
-      </c>
-      <c r="J130">
-        <v>7</v>
-      </c>
-      <c r="K130">
-        <v>0.68</v>
-      </c>
-      <c r="L130">
-        <v>0.12</v>
-      </c>
-      <c r="M130">
-        <v>129</v>
-      </c>
-      <c r="N130">
-        <v>11</v>
-      </c>
       <c r="O130">
-        <v>53207</v>
+        <v>54836</v>
       </c>
       <c r="P130">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q130">
         <v>100</v>
       </c>
       <c r="R130">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S130" s="1">
-        <v>10.9</v>
+        <v>0.11</v>
       </c>
       <c r="T130" s="1">
-        <v>1.0999999999999999E-2</v>
+        <v>0.12</v>
       </c>
       <c r="U130">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="V130">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C131">
-        <v>1001</v>
+        <v>49004</v>
       </c>
       <c r="D131">
-        <v>653.4</v>
+        <v>646</v>
       </c>
       <c r="E131">
+        <v>3</v>
+      </c>
+      <c r="F131">
+        <v>7.9</v>
+      </c>
+      <c r="G131">
         <v>0.5</v>
       </c>
-      <c r="F131">
-        <v>6.1</v>
-      </c>
-      <c r="G131">
-        <v>1.43</v>
-      </c>
       <c r="H131">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="I131">
-        <v>21.49</v>
+        <v>16</v>
       </c>
       <c r="J131">
-        <v>0.23</v>
+        <v>7</v>
       </c>
       <c r="K131">
-        <v>0.22600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="L131">
+        <v>0.12</v>
+      </c>
+      <c r="M131">
+        <v>129</v>
+      </c>
+      <c r="N131">
+        <v>11</v>
+      </c>
+      <c r="O131">
+        <v>53207</v>
+      </c>
+      <c r="P131">
+        <v>5</v>
+      </c>
+      <c r="Q131">
+        <v>100</v>
+      </c>
+      <c r="R131">
+        <v>50</v>
+      </c>
+      <c r="S131" s="1">
+        <v>10.9</v>
+      </c>
+      <c r="T131" s="1">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="M131">
-        <v>88</v>
-      </c>
-      <c r="N131">
-        <v>3</v>
-      </c>
-      <c r="O131">
-        <v>48784</v>
-      </c>
-      <c r="P131">
-        <v>4</v>
-      </c>
-      <c r="Q131">
-        <v>188.1</v>
-      </c>
-      <c r="R131">
-        <v>2</v>
-      </c>
-      <c r="S131" s="1">
-        <v>0.621</v>
-      </c>
-      <c r="T131" s="1">
-        <v>0.02</v>
-      </c>
       <c r="U131">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="V131">
         <v>23</v>
@@ -5152,1433 +5180,1495 @@
     </row>
     <row r="132" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C132">
-        <v>14012</v>
+        <v>1001</v>
       </c>
       <c r="D132">
-        <v>762</v>
+        <v>653.4</v>
       </c>
       <c r="E132">
+        <v>0.5</v>
+      </c>
+      <c r="F132">
+        <v>6.1</v>
+      </c>
+      <c r="G132">
+        <v>1.43</v>
+      </c>
+      <c r="H132">
+        <v>0.17</v>
+      </c>
+      <c r="I132">
+        <v>21.49</v>
+      </c>
+      <c r="J132">
+        <v>0.23</v>
+      </c>
+      <c r="K132">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="L132">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="M132">
+        <v>88</v>
+      </c>
+      <c r="N132">
+        <v>3</v>
+      </c>
+      <c r="O132">
+        <v>48784</v>
+      </c>
+      <c r="P132">
         <v>4</v>
       </c>
-      <c r="F132">
-        <v>5.7</v>
-      </c>
-      <c r="G132">
-        <v>3.6</v>
-      </c>
-      <c r="H132">
-        <v>0.3</v>
-      </c>
-      <c r="I132">
-        <v>7</v>
-      </c>
-      <c r="J132">
-        <v>0.5</v>
-      </c>
-      <c r="K132">
-        <v>0.13</v>
-      </c>
-      <c r="L132">
-        <v>0.05</v>
-      </c>
-      <c r="M132">
-        <v>193</v>
-      </c>
-      <c r="N132">
-        <v>24</v>
-      </c>
-      <c r="O132">
-        <v>55610</v>
-      </c>
-      <c r="P132">
-        <v>50</v>
-      </c>
       <c r="Q132">
-        <v>73</v>
+        <v>188.1</v>
       </c>
       <c r="R132">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S132" s="1">
-        <v>2.7E-2</v>
+        <v>0.621</v>
       </c>
       <c r="T132" s="1">
-        <v>6.0000000000000001E-3</v>
+        <v>0.02</v>
       </c>
       <c r="U132">
-        <v>1.37</v>
+        <v>0.65</v>
       </c>
       <c r="V132">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C133">
-        <v>23009</v>
+        <v>14012</v>
       </c>
       <c r="D133">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="E133">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F133">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="G133">
-        <v>2.2200000000000002</v>
+        <v>3.6</v>
       </c>
       <c r="H133">
-        <v>0.14000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="I133">
-        <v>7.04</v>
+        <v>7</v>
       </c>
       <c r="J133">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K133">
-        <v>0.30199999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="L133">
-        <v>2.4E-2</v>
+        <v>0.05</v>
       </c>
       <c r="M133">
-        <v>291</v>
+        <v>193</v>
       </c>
       <c r="N133">
+        <v>24</v>
+      </c>
+      <c r="O133">
+        <v>55610</v>
+      </c>
+      <c r="P133">
+        <v>50</v>
+      </c>
+      <c r="Q133">
+        <v>73</v>
+      </c>
+      <c r="R133">
         <v>5</v>
       </c>
-      <c r="O133">
-        <v>53411</v>
-      </c>
-      <c r="P133">
-        <v>12</v>
-      </c>
-      <c r="Q133">
-        <v>71.099999999999994</v>
-      </c>
-      <c r="R133">
-        <v>2.1</v>
-      </c>
       <c r="S133" s="1">
-        <v>2.41E-2</v>
+        <v>2.7E-2</v>
       </c>
       <c r="T133" s="1">
-        <v>2.0999999999999999E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="U133">
-        <v>0.65</v>
+        <v>1.37</v>
       </c>
       <c r="V133">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="134" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C134">
-        <v>33005</v>
+        <v>23009</v>
       </c>
       <c r="D134">
-        <v>839</v>
+        <v>771</v>
       </c>
       <c r="E134">
+        <v>3</v>
+      </c>
+      <c r="F134">
+        <v>7.2</v>
+      </c>
+      <c r="G134">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="H134">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I134">
+        <v>7.04</v>
+      </c>
+      <c r="J134">
+        <v>0.2</v>
+      </c>
+      <c r="K134">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="L134">
+        <v>2.4E-2</v>
+      </c>
+      <c r="M134">
+        <v>291</v>
+      </c>
+      <c r="N134">
         <v>5</v>
       </c>
-      <c r="F134">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="G134">
-        <v>2.8</v>
-      </c>
-      <c r="H134">
-        <v>0.5</v>
-      </c>
-      <c r="I134">
-        <v>20.3</v>
-      </c>
-      <c r="J134">
-        <v>0.8</v>
-      </c>
-      <c r="K134">
-        <v>0.26</v>
-      </c>
-      <c r="L134">
-        <v>0.03</v>
-      </c>
-      <c r="M134">
-        <v>165</v>
-      </c>
-      <c r="N134">
-        <v>8</v>
-      </c>
       <c r="O134">
-        <v>51882</v>
+        <v>53411</v>
       </c>
       <c r="P134">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q134">
-        <v>226</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="R134">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="S134" s="1">
-        <v>0.66</v>
+        <v>2.41E-2</v>
       </c>
       <c r="T134" s="1">
-        <v>0.08</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="U134">
-        <v>1.73</v>
+        <v>0.65</v>
       </c>
       <c r="V134">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C135">
-        <v>1010</v>
+        <v>33005</v>
       </c>
       <c r="D135">
-        <v>1144</v>
+        <v>839</v>
       </c>
       <c r="E135">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F135">
-        <v>7.7</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G135">
-        <v>1.1000000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="H135">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I135">
-        <v>7.2</v>
+        <v>20.3</v>
       </c>
       <c r="J135">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K135">
-        <v>0.55000000000000004</v>
+        <v>0.26</v>
       </c>
       <c r="L135">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="M135">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="N135">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O135">
-        <v>53065</v>
+        <v>51882</v>
       </c>
       <c r="P135">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q135">
-        <v>95</v>
+        <v>226</v>
       </c>
       <c r="R135">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S135" s="1">
-        <v>2.5999999999999999E-2</v>
+        <v>0.66</v>
       </c>
       <c r="T135" s="1">
-        <v>7.0000000000000001E-3</v>
+        <v>0.08</v>
       </c>
       <c r="U135">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="V135">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C136">
-        <v>9026</v>
+        <v>1010</v>
       </c>
       <c r="D136">
-        <v>1240</v>
+        <v>1144</v>
       </c>
       <c r="E136">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F136">
-        <v>1.8</v>
+        <v>7.7</v>
       </c>
       <c r="G136">
-        <v>3.64</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H136">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="I136">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="J136">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K136">
-        <v>0.35</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L136">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="M136">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="N136">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O136">
-        <v>51700</v>
+        <v>53065</v>
       </c>
       <c r="P136">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q136">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="R136">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S136" s="1">
-        <v>6.6E-3</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="T136" s="1">
-        <v>1.8E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="U136">
-        <v>0.39</v>
+        <v>1.56</v>
       </c>
       <c r="V136">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C137">
-        <v>62010</v>
+        <v>9026</v>
       </c>
       <c r="D137">
-        <v>1332</v>
+        <v>1240</v>
       </c>
       <c r="E137">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F137">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="G137">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="H137">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="I137">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J137">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K137">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="L137">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="M137">
-        <v>338</v>
+        <v>99</v>
       </c>
       <c r="N137">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O137">
-        <v>54382</v>
+        <v>51700</v>
       </c>
       <c r="P137">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="Q137">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="R137">
         <v>6</v>
       </c>
       <c r="S137" s="1">
-        <v>1.72E-2</v>
+        <v>6.6E-3</v>
       </c>
       <c r="T137" s="1">
-        <v>2.5000000000000001E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="U137">
-        <v>0.79</v>
+        <v>0.39</v>
       </c>
       <c r="V137">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C138">
-        <v>27011</v>
+        <v>62010</v>
       </c>
       <c r="D138">
-        <v>1340</v>
+        <v>1332</v>
       </c>
       <c r="E138">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F138">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G138">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H138">
+        <v>0.2</v>
+      </c>
+      <c r="I138">
+        <v>7</v>
+      </c>
+      <c r="J138">
         <v>0.3</v>
       </c>
-      <c r="I138">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="J138">
-        <v>1.1000000000000001</v>
-      </c>
       <c r="K138">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="L138">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="M138">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="N138">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O138">
-        <v>52240</v>
+        <v>54382</v>
       </c>
       <c r="P138">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="Q138">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="R138">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S138" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>1.72E-2</v>
       </c>
       <c r="T138" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="U138">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="V138">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="139" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C139">
-        <v>4008</v>
+        <v>27011</v>
       </c>
       <c r="D139">
-        <v>1449</v>
+        <v>1340</v>
       </c>
       <c r="E139">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F139">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="G139">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="H139">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="I139">
-        <v>5.13</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J139">
-        <v>0.13</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K139">
-        <v>0.06</v>
+        <v>0.77</v>
       </c>
       <c r="L139">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="M139">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="N139">
+        <v>13</v>
+      </c>
+      <c r="O139">
+        <v>52240</v>
+      </c>
+      <c r="P139">
         <v>30</v>
       </c>
-      <c r="O139">
-        <v>50710</v>
-      </c>
-      <c r="P139">
-        <v>130</v>
-      </c>
       <c r="Q139">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="R139">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="S139" s="1">
-        <v>2.01E-2</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="T139" s="1">
-        <v>1.5E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U139">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="V139">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C140">
-        <v>1006</v>
+        <v>4008</v>
       </c>
       <c r="D140">
-        <v>1524</v>
+        <v>1449</v>
       </c>
       <c r="E140">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F140">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="G140">
-        <v>2.73</v>
+        <v>1.22</v>
       </c>
       <c r="H140">
+        <v>0.09</v>
+      </c>
+      <c r="I140">
+        <v>5.13</v>
+      </c>
+      <c r="J140">
         <v>0.13</v>
       </c>
-      <c r="I140">
-        <v>5.37</v>
-      </c>
-      <c r="J140">
-        <v>0.18</v>
-      </c>
       <c r="K140">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="L140">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="M140">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="N140">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O140">
-        <v>49770</v>
+        <v>50710</v>
       </c>
       <c r="P140">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="Q140">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="R140">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S140" s="1">
-        <v>2.2499999999999999E-2</v>
+        <v>2.01E-2</v>
       </c>
       <c r="T140" s="1">
-        <v>2.2000000000000001E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="U140">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="V140">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="141" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C141">
-        <v>77007</v>
+        <v>1006</v>
       </c>
       <c r="D141">
-        <v>1560</v>
+        <v>1524</v>
       </c>
       <c r="E141">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F141">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="G141">
-        <v>1.56</v>
+        <v>2.73</v>
       </c>
       <c r="H141">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="I141">
-        <v>3.9</v>
+        <v>5.37</v>
       </c>
       <c r="J141">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="K141">
-        <v>0.48</v>
+        <v>0.24</v>
       </c>
       <c r="L141">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="M141">
-        <v>298</v>
+        <v>131</v>
       </c>
       <c r="N141">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O141">
-        <v>53500</v>
+        <v>49770</v>
       </c>
       <c r="P141">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q141">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="R141">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="S141" s="1">
-        <v>6.6E-3</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="T141" s="1">
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="U141">
-        <v>0.83</v>
+        <v>0.49</v>
       </c>
       <c r="V141">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C142">
-        <v>9002</v>
+        <v>77007</v>
       </c>
       <c r="D142">
-        <v>1584</v>
+        <v>1560</v>
       </c>
       <c r="E142">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F142">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G142">
-        <v>1.99</v>
+        <v>1.56</v>
       </c>
       <c r="H142">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="I142">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="J142">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="K142">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="L142">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="M142">
+        <v>298</v>
+      </c>
+      <c r="N142">
+        <v>11</v>
+      </c>
+      <c r="O142">
+        <v>53500</v>
+      </c>
+      <c r="P142">
+        <v>50</v>
+      </c>
+      <c r="Q142">
         <v>74</v>
       </c>
-      <c r="N142">
-        <v>7</v>
-      </c>
-      <c r="O142">
-        <v>50031</v>
-      </c>
-      <c r="P142">
-        <v>22</v>
-      </c>
-      <c r="Q142">
-        <v>79</v>
-      </c>
       <c r="R142">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S142" s="1">
-        <v>7.9000000000000008E-3</v>
+        <v>6.6E-3</v>
       </c>
       <c r="T142" s="1">
-        <v>1.5E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="U142">
-        <v>0.43</v>
+        <v>0.83</v>
       </c>
       <c r="V142">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C143">
-        <v>40006</v>
+        <v>9002</v>
       </c>
       <c r="D143">
-        <v>2070</v>
+        <v>1584</v>
       </c>
       <c r="E143">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F143">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="G143">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="H143">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="I143">
-        <v>4.4000000000000004</v>
+        <v>3.94</v>
       </c>
       <c r="J143">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="K143">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="L143">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="M143">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="N143">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O143">
-        <v>51560</v>
+        <v>50031</v>
       </c>
       <c r="P143">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Q143">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="R143">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S143" s="1">
-        <v>1.4999999999999999E-2</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="T143" s="1">
-        <v>4.0000000000000001E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="U143">
-        <v>0.81</v>
+        <v>0.43</v>
       </c>
       <c r="V143">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C144">
-        <v>17008</v>
+        <v>40006</v>
       </c>
       <c r="D144">
-        <v>2230</v>
+        <v>2070</v>
       </c>
       <c r="E144">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F144">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="G144">
-        <v>2.99</v>
+        <v>2.09</v>
       </c>
       <c r="H144">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="I144">
-        <v>3.54</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J144">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="K144">
-        <v>0.16</v>
+        <v>0.38</v>
       </c>
       <c r="L144">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="M144">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="N144">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O144">
-        <v>54710</v>
+        <v>51560</v>
       </c>
       <c r="P144">
         <v>90</v>
       </c>
       <c r="Q144">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="R144">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S144" s="1">
-        <v>9.7999999999999997E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="T144" s="1">
-        <v>1.6000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="U144">
-        <v>0.46</v>
+        <v>0.81</v>
       </c>
       <c r="V144">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="145" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C145">
-        <v>2008</v>
+        <v>17008</v>
       </c>
       <c r="D145">
-        <v>2379</v>
+        <v>2230</v>
       </c>
       <c r="E145">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="F145">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="G145">
-        <v>1.79</v>
+        <v>2.99</v>
       </c>
       <c r="H145">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="I145">
-        <v>5.76</v>
+        <v>3.54</v>
       </c>
       <c r="J145">
+        <v>0.19</v>
+      </c>
+      <c r="K145">
         <v>0.16</v>
       </c>
-      <c r="K145">
-        <v>0.24</v>
-      </c>
       <c r="L145">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M145">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="N145">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O145">
-        <v>52040</v>
+        <v>54710</v>
       </c>
       <c r="P145">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q145">
-        <v>183</v>
+        <v>107</v>
       </c>
       <c r="R145">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S145" s="1">
-        <v>4.2999999999999997E-2</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="T145" s="1">
-        <v>4.0000000000000001E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="U145">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="V145">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C146">
-        <v>22006</v>
+        <v>2008</v>
       </c>
       <c r="D146">
-        <v>2390</v>
+        <v>2379</v>
       </c>
       <c r="E146">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F146">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="G146">
-        <v>2.5499999999999998</v>
+        <v>1.79</v>
       </c>
       <c r="H146">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I146">
+        <v>5.76</v>
+      </c>
+      <c r="J146">
+        <v>0.16</v>
+      </c>
+      <c r="K146">
         <v>0.24</v>
-      </c>
-      <c r="I146">
-        <v>5.5</v>
-      </c>
-      <c r="J146">
-        <v>0.4</v>
-      </c>
-      <c r="K146">
-        <v>0.59</v>
       </c>
       <c r="L146">
         <v>0.04</v>
       </c>
       <c r="M146">
-        <v>311</v>
+        <v>143</v>
       </c>
       <c r="N146">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O146">
-        <v>51960</v>
+        <v>52040</v>
       </c>
       <c r="P146">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q146">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="R146">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S146" s="1">
-        <v>2.1999999999999999E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="T146" s="1">
-        <v>5.0000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="U146">
-        <v>0.82</v>
+        <v>0.51</v>
       </c>
       <c r="V146">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="147" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C147">
-        <v>20008</v>
+        <v>22006</v>
       </c>
       <c r="D147">
-        <v>2540</v>
+        <v>2390</v>
       </c>
       <c r="E147">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="F147">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G147">
-        <v>3.3</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="H147">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="I147">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="J147">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K147">
-        <v>0.37</v>
+        <v>0.59</v>
       </c>
       <c r="L147">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M147">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="N147">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O147">
-        <v>55630</v>
+        <v>51960</v>
       </c>
       <c r="P147">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q147">
-        <v>258</v>
+        <v>147</v>
       </c>
       <c r="R147">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S147" s="1">
-        <v>0.106</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="T147" s="1">
-        <v>2.1999999999999999E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="U147">
-        <v>1.26</v>
+        <v>0.82</v>
       </c>
       <c r="V147">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="148" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C148">
-        <v>56010</v>
+        <v>20008</v>
       </c>
       <c r="D148">
-        <v>2600</v>
+        <v>2540</v>
       </c>
       <c r="E148">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="F148">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G148">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="H148">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="I148">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="J148">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="K148">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="L148">
-        <v>0.19</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M148">
-        <v>90</v>
+        <v>283</v>
       </c>
       <c r="N148">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="O148">
-        <v>54510</v>
+        <v>55630</v>
       </c>
       <c r="P148">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="Q148">
-        <v>320</v>
+        <v>258</v>
       </c>
       <c r="R148">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="S148" s="1">
-        <v>0.2</v>
+        <v>0.106</v>
       </c>
       <c r="T148" s="1">
-        <v>0.19</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="U148">
-        <v>0.77</v>
+        <v>1.26</v>
       </c>
       <c r="V148">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C149">
-        <v>2012</v>
+        <v>56010</v>
       </c>
       <c r="D149">
-        <v>2920</v>
+        <v>2600</v>
       </c>
       <c r="E149">
+        <v>40</v>
+      </c>
+      <c r="F149">
+        <v>1.5</v>
+      </c>
+      <c r="G149">
+        <v>2.6</v>
+      </c>
+      <c r="H149">
+        <v>1.9</v>
+      </c>
+      <c r="I149">
+        <v>9</v>
+      </c>
+      <c r="J149">
+        <v>3</v>
+      </c>
+      <c r="K149">
+        <v>0.23</v>
+      </c>
+      <c r="L149">
+        <v>0.19</v>
+      </c>
+      <c r="M149">
+        <v>90</v>
+      </c>
+      <c r="N149">
         <v>30</v>
       </c>
-      <c r="F149">
-        <v>1.8</v>
-      </c>
-      <c r="G149">
-        <v>2.64</v>
-      </c>
-      <c r="H149">
-        <v>0.16</v>
-      </c>
-      <c r="I149">
-        <v>6.01</v>
-      </c>
-      <c r="J149">
+      <c r="O149">
+        <v>54510</v>
+      </c>
+      <c r="P149">
+        <v>150</v>
+      </c>
+      <c r="Q149">
+        <v>320</v>
+      </c>
+      <c r="R149">
+        <v>110</v>
+      </c>
+      <c r="S149" s="1">
         <v>0.2</v>
       </c>
-      <c r="K149">
-        <v>0.39</v>
-      </c>
-      <c r="L149">
-        <v>0.03</v>
-      </c>
-      <c r="M149">
-        <v>19</v>
-      </c>
-      <c r="N149">
-        <v>4</v>
-      </c>
-      <c r="O149">
-        <v>51860</v>
-      </c>
-      <c r="P149">
-        <v>30</v>
-      </c>
-      <c r="Q149">
-        <v>223</v>
-      </c>
-      <c r="R149">
-        <v>8</v>
-      </c>
-      <c r="S149" s="1">
-        <v>5.0999999999999997E-2</v>
-      </c>
       <c r="T149" s="1">
-        <v>5.0000000000000001E-3</v>
+        <v>0.19</v>
       </c>
       <c r="U149">
-        <v>0.41</v>
+        <v>0.77</v>
       </c>
       <c r="V149">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C150">
-        <v>6002</v>
+        <v>2012</v>
       </c>
       <c r="D150">
-        <v>3360</v>
+        <v>2920</v>
       </c>
       <c r="E150">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F150">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="G150">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="H150">
+        <v>0.16</v>
+      </c>
+      <c r="I150">
+        <v>6.01</v>
+      </c>
+      <c r="J150">
         <v>0.2</v>
       </c>
-      <c r="I150">
-        <v>4.7</v>
-      </c>
-      <c r="J150">
-        <v>0.6</v>
-      </c>
       <c r="K150">
-        <v>0.72</v>
+        <v>0.39</v>
       </c>
       <c r="L150">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="M150">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="N150">
         <v>4</v>
       </c>
       <c r="O150">
-        <v>48249</v>
+        <v>51860</v>
       </c>
       <c r="P150">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q150">
-        <v>151</v>
+        <v>223</v>
       </c>
       <c r="R150">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="S150" s="1">
-        <v>1.2E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="T150" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="U150">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="V150">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C151">
-        <v>20003</v>
+        <v>6002</v>
       </c>
       <c r="D151">
-        <v>3540</v>
+        <v>3360</v>
       </c>
       <c r="E151">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="F151">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G151">
-        <v>2.2999999999999998</v>
+        <v>2.19</v>
       </c>
       <c r="H151">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I151">
-        <v>3.17</v>
+        <v>4.7</v>
       </c>
       <c r="J151">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="K151">
-        <v>0.08</v>
+        <v>0.72</v>
       </c>
       <c r="L151">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="M151">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="N151">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="O151">
-        <v>53300</v>
+        <v>48249</v>
       </c>
       <c r="P151">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="Q151">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="R151">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="S151" s="1">
-        <v>1.0999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="T151" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="U151">
-        <v>0.64</v>
+        <v>0.49</v>
       </c>
       <c r="V151">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C152">
-        <v>6006</v>
+        <v>20003</v>
       </c>
       <c r="D152">
-        <v>5200</v>
+        <v>3540</v>
       </c>
       <c r="E152">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F152">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G152">
-        <v>0.64</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="H152">
+        <v>0.3</v>
+      </c>
+      <c r="I152">
+        <v>3.17</v>
+      </c>
+      <c r="J152">
+        <v>0.25</v>
+      </c>
+      <c r="K152">
+        <v>0.08</v>
+      </c>
+      <c r="L152">
         <v>0.12</v>
       </c>
-      <c r="I152">
-        <v>3.44</v>
-      </c>
-      <c r="J152">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K152">
-        <v>0.1</v>
-      </c>
-      <c r="L152">
-        <v>0.04</v>
-      </c>
       <c r="M152">
-        <v>344</v>
+        <v>40</v>
       </c>
       <c r="N152">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="O152">
-        <v>56200</v>
+        <v>53300</v>
       </c>
       <c r="P152">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="Q152">
-        <v>245</v>
+        <v>154</v>
       </c>
       <c r="R152">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S152" s="1">
-        <v>2.1999999999999999E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="T152" s="1">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="U152">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="V152">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C153">
-        <v>3011</v>
+        <v>6006</v>
       </c>
       <c r="D153">
-        <v>7369</v>
+        <v>5200</v>
       </c>
       <c r="E153">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="F153">
-        <v>1.1000000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="G153">
-        <v>3.02</v>
+        <v>0.64</v>
       </c>
       <c r="H153">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I153">
-        <v>4.28</v>
+        <v>3.44</v>
       </c>
       <c r="J153">
-        <v>0.11</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K153">
-        <v>0.60799999999999998</v>
+        <v>0.1</v>
       </c>
       <c r="L153">
-        <v>1.2E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M153">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N153">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O153">
-        <v>54980</v>
+        <v>56200</v>
       </c>
       <c r="P153">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="Q153">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="R153">
         <v>10</v>
       </c>
       <c r="S153" s="1">
-        <v>2.9899999999999999E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="T153" s="1">
-        <v>2.3E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="U153">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="V153">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="154" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C154">
-        <v>11006</v>
+        <v>3011</v>
       </c>
       <c r="D154">
-        <v>7810</v>
+        <v>7369</v>
       </c>
       <c r="E154">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F154">
         <v>1.1000000000000001</v>
       </c>
       <c r="G154">
+        <v>3.02</v>
+      </c>
+      <c r="H154">
+        <v>0.11</v>
+      </c>
+      <c r="I154">
+        <v>4.28</v>
+      </c>
+      <c r="J154">
+        <v>0.11</v>
+      </c>
+      <c r="K154">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="L154">
+        <v>1.2E-2</v>
+      </c>
+      <c r="M154">
+        <v>345</v>
+      </c>
+      <c r="N154">
+        <v>4</v>
+      </c>
+      <c r="O154">
+        <v>54980</v>
+      </c>
+      <c r="P154">
+        <v>30</v>
+      </c>
+      <c r="Q154">
+        <v>344</v>
+      </c>
+      <c r="R154">
+        <v>10</v>
+      </c>
+      <c r="S154" s="1">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="T154" s="1">
+        <v>2.3E-3</v>
+      </c>
+      <c r="U154">
+        <v>0.32</v>
+      </c>
+      <c r="V154">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="155" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="C155">
+        <v>11006</v>
+      </c>
+      <c r="D155">
+        <v>7810</v>
+      </c>
+      <c r="E155">
+        <v>60</v>
+      </c>
+      <c r="F155">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G155">
         <v>2.35</v>
       </c>
-      <c r="H154">
+      <c r="H155">
         <v>0.22</v>
       </c>
-      <c r="I154">
+      <c r="I155">
         <v>3.8</v>
       </c>
-      <c r="J154">
+      <c r="J155">
         <v>0.3</v>
       </c>
-      <c r="K154">
+      <c r="K155">
         <v>0.67</v>
       </c>
-      <c r="L154">
+      <c r="L155">
         <v>0.04</v>
       </c>
-      <c r="M154">
+      <c r="M155">
         <v>172</v>
       </c>
-      <c r="N154">
+      <c r="N155">
         <v>7</v>
       </c>
-      <c r="O154">
+      <c r="O155">
         <v>48470</v>
       </c>
-      <c r="P154">
+      <c r="P155">
         <v>70</v>
       </c>
-      <c r="Q154">
+      <c r="Q155">
         <v>310</v>
       </c>
-      <c r="R154">
+      <c r="R155">
         <v>30</v>
       </c>
-      <c r="S154" s="1">
+      <c r="S155" s="1">
         <v>1.9E-2</v>
       </c>
-      <c r="T154" s="1">
+      <c r="T155" s="1">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="U154">
+      <c r="U155">
         <v>0.7</v>
       </c>
-      <c r="V154">
+      <c r="V155">
         <v>32</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C77:V154">
-    <sortCondition ref="D77:D154"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C78:V155">
+    <sortCondition ref="D78:D155"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
+++ b/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpenev/projects/git/CircularizationDissipationConstraints/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64123CA-8ED9-0A4F-AFF2-D3A4171914AE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219EC134-4FBF-3749-B180-F3817080C865}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15940" yWindow="5380" windowWidth="31560" windowHeight="22480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Milliman_et_al_2014_WIYN_single" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1779,7 +1790,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:22" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="B78" s="13" t="s">
         <v>101</v>
       </c>
@@ -1845,11 +1856,11 @@
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="7" t="s">
         <v>103</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>49002</v>
@@ -1912,7 +1923,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:22" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="C80" s="11">
         <v>14008</v>
       </c>
@@ -1974,7 +1985,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:22" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="B81" s="13" t="s">
         <v>102</v>
       </c>
@@ -2040,10 +2051,10 @@
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="7" t="s">
         <v>102</v>
       </c>
       <c r="C82">
@@ -2108,10 +2119,10 @@
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="7" t="s">
         <v>102</v>
       </c>
       <c r="C83">
@@ -2175,7 +2186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:22" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="B84"/>
       <c r="C84" s="11">
         <v>35025</v>
@@ -2239,10 +2250,10 @@
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="7" t="s">
         <v>102</v>
       </c>
       <c r="C85">
@@ -2310,7 +2321,7 @@
       <c r="A86" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="8" t="s">
         <v>102</v>
       </c>
       <c r="C86">
@@ -2631,10 +2642,10 @@
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="8" t="s">
         <v>102</v>
       </c>
       <c r="C91">

--- a/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
+++ b/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpenev/projects/git/CircularizationDissipationConstraints/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219EC134-4FBF-3749-B180-F3817080C865}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B33BDB3-EB8A-BB42-A5F8-405605E4B015}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15940" yWindow="5380" windowWidth="31560" windowHeight="22480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2318,7 +2318,7 @@
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="7" t="s">
         <v>103</v>
       </c>
       <c r="B86" s="8" t="s">
@@ -2642,7 +2642,7 @@
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="8" t="s">
         <v>103</v>
       </c>
       <c r="B91" s="8" t="s">

--- a/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
+++ b/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kpenev/projects/git/CircularizationDissipationConstraints/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B33BDB3-EB8A-BB42-A5F8-405605E4B015}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90526A76-AEF2-884C-B873-6A6AA7D3D816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15940" yWindow="5380" windowWidth="31560" windowHeight="22480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="480" windowWidth="33600" windowHeight="20540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Milliman_et_al_2014_WIYN_single" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
   <si>
     <t>#</t>
   </si>
@@ -321,9 +321,6 @@
     <t>bold red text</t>
   </si>
   <si>
-    <t>System is not a member of NGC6819</t>
-  </si>
-  <si>
     <t>Q=pworlaw</t>
   </si>
   <si>
@@ -339,17 +336,17 @@
     <t>kartof</t>
   </si>
   <si>
-    <t>ganymede</t>
-  </si>
-  <si>
     <t>stampede</t>
+  </si>
+  <si>
+    <t>System is not a member of M35</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -515,6 +512,12 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFD261CE"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -885,7 +888,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -901,6 +904,15 @@
     <xf numFmtId="11" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1263,6 +1275,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V155"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="11" max="11" width="10.83203125" style="7"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1647,10 +1662,10 @@
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A74" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B74" t="s">
         <v>99</v>
-      </c>
-      <c r="B74" t="s">
-        <v>100</v>
       </c>
       <c r="C74" s="4"/>
     </row>
@@ -1659,16 +1674,16 @@
         <v>95</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C75" s="4"/>
     </row>
     <row r="76" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>81</v>
@@ -1694,7 +1709,7 @@
       <c r="J76" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="K76" s="18" t="s">
         <v>81</v>
       </c>
       <c r="L76" s="2" t="s">
@@ -1753,7 +1768,7 @@
       <c r="J77" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="K77" s="18" t="s">
         <v>69</v>
       </c>
       <c r="L77" s="2" t="s">
@@ -1792,7 +1807,7 @@
     </row>
     <row r="78" spans="1:22" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="B78" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C78" s="13">
         <v>25011</v>
@@ -1818,7 +1833,7 @@
       <c r="J78" s="13">
         <v>0.4</v>
       </c>
-      <c r="K78" s="13">
+      <c r="K78" s="19">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="L78" s="13">
@@ -1857,11 +1872,9 @@
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>102</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B79" s="15"/>
       <c r="C79">
         <v>49002</v>
       </c>
@@ -1886,7 +1899,7 @@
       <c r="J79">
         <v>1.2</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="7">
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="L79">
@@ -1924,6 +1937,8 @@
       </c>
     </row>
     <row r="80" spans="1:22" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="15"/>
+      <c r="B80" s="16"/>
       <c r="C80" s="11">
         <v>14008</v>
       </c>
@@ -1948,7 +1963,7 @@
       <c r="J80" s="11">
         <v>1.3</v>
       </c>
-      <c r="K80" s="11">
+      <c r="K80" s="20">
         <v>0.02</v>
       </c>
       <c r="L80" s="11">
@@ -1986,9 +2001,8 @@
       </c>
     </row>
     <row r="81" spans="1:22" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="13" t="s">
-        <v>102</v>
-      </c>
+      <c r="A81" s="15"/>
+      <c r="B81" s="17"/>
       <c r="C81" s="13">
         <v>32006</v>
       </c>
@@ -2013,7 +2027,7 @@
       <c r="J81" s="13">
         <v>0.3</v>
       </c>
-      <c r="K81" s="13">
+      <c r="K81" s="19">
         <v>0.05</v>
       </c>
       <c r="L81" s="13">
@@ -2052,11 +2066,9 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A82" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>102</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B82" s="15"/>
       <c r="C82">
         <v>66004</v>
       </c>
@@ -2081,7 +2093,7 @@
       <c r="J82">
         <v>0.7</v>
       </c>
-      <c r="K82">
+      <c r="K82" s="7">
         <v>1.6E-2</v>
       </c>
       <c r="L82">
@@ -2119,12 +2131,10 @@
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A83" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>102</v>
-      </c>
+      <c r="A83" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83" s="15"/>
       <c r="C83">
         <v>13001</v>
       </c>
@@ -2149,7 +2159,7 @@
       <c r="J83">
         <v>1</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="7">
         <v>4.7E-2</v>
       </c>
       <c r="L83">
@@ -2187,7 +2197,8 @@
       </c>
     </row>
     <row r="84" spans="1:22" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B84"/>
+      <c r="A84" s="15"/>
+      <c r="B84" s="15"/>
       <c r="C84" s="11">
         <v>35025</v>
       </c>
@@ -2212,7 +2223,7 @@
       <c r="J84" s="11">
         <v>0.5</v>
       </c>
-      <c r="K84" s="11">
+      <c r="K84" s="20">
         <v>0.20799999999999999</v>
       </c>
       <c r="L84" s="11">
@@ -2250,12 +2261,10 @@
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A85" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>102</v>
-      </c>
+      <c r="A85" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B85" s="15"/>
       <c r="C85">
         <v>60006</v>
       </c>
@@ -2280,7 +2289,7 @@
       <c r="J85">
         <v>0.22</v>
       </c>
-      <c r="K85">
+      <c r="K85" s="7">
         <v>1.9E-2</v>
       </c>
       <c r="L85">
@@ -2318,12 +2327,10 @@
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A86" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>102</v>
-      </c>
+      <c r="A86" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B86" s="15"/>
       <c r="C86">
         <v>57004</v>
       </c>
@@ -2348,7 +2355,7 @@
       <c r="J86">
         <v>0.22</v>
       </c>
-      <c r="K86">
+      <c r="K86" s="7">
         <v>0.123</v>
       </c>
       <c r="L86">
@@ -2385,138 +2392,138 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B87" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C87">
+    <row r="87" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="17"/>
+      <c r="C87" s="13">
         <v>33002</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="13">
         <v>10.9025</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="13">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="13">
         <v>232.3</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="13">
         <v>3.1</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="13">
         <v>0.5</v>
       </c>
-      <c r="I87">
+      <c r="I87" s="13">
         <v>40.5</v>
       </c>
-      <c r="J87">
+      <c r="J87" s="13">
         <v>0.5</v>
       </c>
-      <c r="K87">
+      <c r="K87" s="19">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="L87">
+      <c r="L87" s="13">
         <v>1.6E-2</v>
       </c>
-      <c r="M87">
+      <c r="M87" s="13">
         <v>10</v>
       </c>
-      <c r="N87">
+      <c r="N87" s="13">
         <v>30</v>
       </c>
-      <c r="O87">
+      <c r="O87" s="13">
         <v>54194.1</v>
       </c>
-      <c r="P87">
+      <c r="P87" s="13">
         <v>1</v>
       </c>
-      <c r="Q87">
+      <c r="Q87" s="13">
         <v>6.07</v>
       </c>
-      <c r="R87">
+      <c r="R87" s="13">
         <v>0.08</v>
       </c>
-      <c r="S87" s="1">
+      <c r="S87" s="13">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="T87" s="1">
+      <c r="T87" s="13">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="U87">
+      <c r="U87" s="13">
         <v>1.56</v>
       </c>
-      <c r="V87">
+      <c r="V87" s="13">
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B88"/>
-      <c r="C88" s="9">
+    <row r="88" spans="1:22" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B88" s="21"/>
+      <c r="C88" s="22">
         <v>46013</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="22">
         <v>14.2111</v>
       </c>
-      <c r="E88" s="9">
+      <c r="E88" s="22">
         <v>1.5E-3</v>
       </c>
-      <c r="F88" s="9">
+      <c r="F88" s="22">
         <v>105.4</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="22">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H88" s="9">
+      <c r="H88" s="22">
         <v>0.3</v>
       </c>
-      <c r="I88" s="9">
+      <c r="I88" s="22">
         <v>10.8</v>
       </c>
-      <c r="J88" s="9">
+      <c r="J88" s="22">
         <v>0.5</v>
       </c>
-      <c r="K88" s="9">
+      <c r="K88" s="23">
         <v>0.53</v>
       </c>
-      <c r="L88" s="9">
+      <c r="L88" s="22">
         <v>0.04</v>
       </c>
-      <c r="M88" s="9">
+      <c r="M88" s="22">
         <v>256</v>
       </c>
-      <c r="N88" s="9">
+      <c r="N88" s="22">
         <v>5</v>
       </c>
-      <c r="O88" s="9">
+      <c r="O88" s="22">
         <v>51878.89</v>
       </c>
-      <c r="P88" s="9">
+      <c r="P88" s="22">
         <v>0.11</v>
       </c>
-      <c r="Q88" s="9">
+      <c r="Q88" s="22">
         <v>1.79</v>
       </c>
-      <c r="R88" s="9">
+      <c r="R88" s="22">
         <v>0.1</v>
       </c>
-      <c r="S88" s="9">
+      <c r="S88" s="22">
         <v>1.1299999999999999E-3</v>
       </c>
-      <c r="T88" s="9">
+      <c r="T88" s="22">
         <v>1.8000000000000001E-4</v>
       </c>
-      <c r="U88" s="9">
+      <c r="U88" s="22">
         <v>1.41</v>
       </c>
-      <c r="V88" s="9">
+      <c r="V88" s="22">
         <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="13" t="s">
-        <v>102</v>
-      </c>
+      <c r="A89" s="17"/>
+      <c r="B89" s="17"/>
       <c r="C89" s="13">
         <v>3002</v>
       </c>
@@ -2541,7 +2548,7 @@
       <c r="J89" s="13">
         <v>0.5</v>
       </c>
-      <c r="K89" s="13">
+      <c r="K89" s="19">
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="L89" s="13">
@@ -2578,76 +2585,77 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B90"/>
-      <c r="C90" s="9">
+    <row r="90" spans="1:22" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" s="21"/>
+      <c r="C90" s="22">
         <v>25004</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="22">
         <v>21.283999999999999</v>
       </c>
-      <c r="E90" s="9">
+      <c r="E90" s="22">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F90" s="9">
+      <c r="F90" s="22">
         <v>138.30000000000001</v>
       </c>
-      <c r="G90" s="9">
+      <c r="G90" s="22">
         <v>1.2</v>
       </c>
-      <c r="H90" s="9">
+      <c r="H90" s="22">
         <v>0.3</v>
       </c>
-      <c r="I90" s="9">
+      <c r="I90" s="22">
         <v>17.53</v>
       </c>
-      <c r="J90" s="9">
+      <c r="J90" s="22">
         <v>0.23</v>
       </c>
-      <c r="K90" s="9">
+      <c r="K90" s="23">
         <v>0.41699999999999998</v>
       </c>
-      <c r="L90" s="9">
+      <c r="L90" s="22">
         <v>1.6E-2</v>
       </c>
-      <c r="M90" s="9">
+      <c r="M90" s="22">
         <v>297.39999999999998</v>
       </c>
-      <c r="N90" s="9">
+      <c r="N90" s="22">
         <v>2.1</v>
       </c>
-      <c r="O90" s="9">
+      <c r="O90" s="22">
         <v>52029.5</v>
       </c>
-      <c r="P90" s="9">
+      <c r="P90" s="22">
         <v>0.21</v>
       </c>
-      <c r="Q90" s="9">
+      <c r="Q90" s="22">
         <v>4.66</v>
       </c>
-      <c r="R90" s="9">
+      <c r="R90" s="22">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="S90" s="9">
+      <c r="S90" s="22">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="T90" s="9">
+      <c r="T90" s="22">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="U90" s="9">
+      <c r="U90" s="22">
         <v>0.48</v>
       </c>
-      <c r="V90" s="9">
+      <c r="V90" s="22">
         <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A91" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>102</v>
-      </c>
+      <c r="A91" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" s="15"/>
       <c r="C91">
         <v>59003</v>
       </c>
@@ -2672,7 +2680,7 @@
       <c r="J91">
         <v>0.4</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="7">
         <v>0.27500000000000002</v>
       </c>
       <c r="L91">
@@ -2709,317 +2717,334 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C92" s="9">
+    <row r="92" spans="1:22" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B92" s="21"/>
+      <c r="C92" s="22">
         <v>31004</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="22">
         <v>22.856999999999999</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E92" s="22">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F92" s="9">
+      <c r="F92" s="22">
         <v>84.3</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G92" s="22">
         <v>2.8</v>
       </c>
-      <c r="H92" s="9">
+      <c r="H92" s="22">
         <v>1.3</v>
       </c>
-      <c r="I92" s="9">
+      <c r="I92" s="22">
         <v>14</v>
       </c>
-      <c r="J92" s="9">
+      <c r="J92" s="22">
         <v>3</v>
       </c>
-      <c r="K92" s="9">
+      <c r="K92" s="23">
         <v>0.39</v>
       </c>
-      <c r="L92" s="9">
+      <c r="L92" s="22">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M92" s="9">
+      <c r="M92" s="22">
         <v>307</v>
       </c>
-      <c r="N92" s="9">
+      <c r="N92" s="22">
         <v>8</v>
       </c>
-      <c r="O92" s="9">
+      <c r="O92" s="22">
         <v>55742.2</v>
       </c>
-      <c r="P92" s="9">
+      <c r="P92" s="22">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q92" s="9">
+      <c r="Q92" s="22">
         <v>4</v>
       </c>
-      <c r="R92" s="9">
+      <c r="R92" s="22">
         <v>0.8</v>
       </c>
-      <c r="S92" s="9">
+      <c r="S92" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="T92" s="9">
+      <c r="T92" s="22">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="U92" s="9">
+      <c r="U92" s="22">
         <v>0.42</v>
       </c>
-      <c r="V92" s="9">
+      <c r="V92" s="22">
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="9">
+    <row r="93" spans="1:22" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="21"/>
+      <c r="C93" s="22">
         <v>21007</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="22">
         <v>23.920999999999999</v>
       </c>
-      <c r="E93" s="9">
+      <c r="E93" s="22">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="F93" s="9">
+      <c r="F93" s="22">
         <v>49.6</v>
       </c>
-      <c r="G93" s="9">
+      <c r="G93" s="22">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H93" s="9">
+      <c r="H93" s="22">
         <v>0.5</v>
       </c>
-      <c r="I93" s="9">
+      <c r="I93" s="22">
         <v>16.2</v>
       </c>
-      <c r="J93" s="9">
+      <c r="J93" s="22">
         <v>0.4</v>
       </c>
-      <c r="K93" s="9">
+      <c r="K93" s="23">
         <v>0.4</v>
       </c>
-      <c r="L93" s="9">
+      <c r="L93" s="22">
         <v>0.03</v>
       </c>
-      <c r="M93" s="9">
+      <c r="M93" s="22">
         <v>248</v>
       </c>
-      <c r="N93" s="9">
+      <c r="N93" s="22">
         <v>6</v>
       </c>
-      <c r="O93" s="9">
+      <c r="O93" s="22">
         <v>52123.3</v>
       </c>
-      <c r="P93" s="9">
+      <c r="P93" s="22">
         <v>0.4</v>
       </c>
-      <c r="Q93" s="9">
+      <c r="Q93" s="22">
         <v>4.87</v>
       </c>
-      <c r="R93" s="9">
+      <c r="R93" s="22">
         <v>0.13</v>
       </c>
-      <c r="S93" s="9">
+      <c r="S93" s="22">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="T93" s="9">
+      <c r="T93" s="22">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="U93" s="9">
+      <c r="U93" s="22">
         <v>0.88</v>
       </c>
-      <c r="V93" s="9">
+      <c r="V93" s="22">
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:22" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C94" s="9">
+    <row r="94" spans="1:22" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="21"/>
+      <c r="C94" s="22">
         <v>35020</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="22">
         <v>24.736999999999998</v>
       </c>
-      <c r="E94" s="9">
+      <c r="E94" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F94" s="9">
+      <c r="F94" s="22">
         <v>45.4</v>
       </c>
-      <c r="G94" s="9">
+      <c r="G94" s="22">
         <v>1.4</v>
       </c>
-      <c r="H94" s="9">
+      <c r="H94" s="22">
         <v>0.17</v>
       </c>
-      <c r="I94" s="9">
+      <c r="I94" s="22">
         <v>12.4</v>
       </c>
-      <c r="J94" s="9">
+      <c r="J94" s="22">
         <v>0.5</v>
       </c>
-      <c r="K94" s="9">
+      <c r="K94" s="23">
         <v>0.36</v>
       </c>
-      <c r="L94" s="9">
+      <c r="L94" s="22">
         <v>0.03</v>
       </c>
-      <c r="M94" s="9">
+      <c r="M94" s="22">
         <v>136</v>
       </c>
-      <c r="N94" s="9">
+      <c r="N94" s="22">
         <v>4</v>
       </c>
-      <c r="O94" s="9">
+      <c r="O94" s="22">
         <v>52042.16</v>
       </c>
-      <c r="P94" s="9">
+      <c r="P94" s="22">
         <v>0.19</v>
       </c>
-      <c r="Q94" s="9">
+      <c r="Q94" s="22">
         <v>3.93</v>
       </c>
-      <c r="R94" s="9">
+      <c r="R94" s="22">
         <v>0.15</v>
       </c>
-      <c r="S94" s="9">
+      <c r="S94" s="22">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="T94" s="9">
+      <c r="T94" s="22">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="U94" s="9">
+      <c r="U94" s="22">
         <v>0.57999999999999996</v>
       </c>
-      <c r="V94" s="9">
+      <c r="V94" s="22">
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C95">
+    <row r="95" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="17"/>
+      <c r="C95" s="13">
         <v>24012</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="13">
         <v>25.526599999999998</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="13">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="13">
         <v>114.6</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="13">
         <v>1.69</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="13">
         <v>0.15</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="13">
         <v>19.100000000000001</v>
       </c>
-      <c r="J95">
+      <c r="J95" s="13">
         <v>0.3</v>
       </c>
-      <c r="K95">
+      <c r="K95" s="19">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="L95">
+      <c r="L95" s="13">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="M95">
+      <c r="M95" s="13">
         <v>120</v>
       </c>
-      <c r="N95">
+      <c r="N95" s="13">
         <v>170</v>
       </c>
-      <c r="O95">
+      <c r="O95" s="13">
         <v>52137</v>
       </c>
-      <c r="P95">
+      <c r="P95" s="13">
         <v>12</v>
       </c>
-      <c r="Q95">
+      <c r="Q95" s="13">
         <v>6.69</v>
       </c>
-      <c r="R95">
+      <c r="R95" s="13">
         <v>0.09</v>
       </c>
-      <c r="S95" s="1">
+      <c r="S95" s="13">
         <v>1.83E-2</v>
       </c>
-      <c r="T95" s="1">
+      <c r="T95" s="13">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="U95">
+      <c r="U95" s="13">
         <v>0.53</v>
       </c>
-      <c r="V95">
+      <c r="V95" s="13">
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="C96">
+    <row r="96" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="17"/>
+      <c r="C96" s="13">
         <v>39013</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="13">
         <v>36.707999999999998</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="13">
         <v>0.01</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="13">
         <v>99.2</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="13">
         <v>2.7</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="13">
         <v>0.6</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="13">
         <v>17.100000000000001</v>
       </c>
-      <c r="J96">
+      <c r="J96" s="13">
         <v>0.8</v>
       </c>
-      <c r="K96">
+      <c r="K96" s="19">
         <v>0.06</v>
       </c>
-      <c r="L96">
+      <c r="L96" s="13">
         <v>0.05</v>
       </c>
-      <c r="M96">
+      <c r="M96" s="13">
         <v>240</v>
       </c>
-      <c r="N96">
+      <c r="N96" s="13">
         <v>40</v>
       </c>
-      <c r="O96">
+      <c r="O96" s="13">
         <v>54427</v>
       </c>
-      <c r="P96">
+      <c r="P96" s="13">
         <v>4</v>
       </c>
-      <c r="Q96">
+      <c r="Q96" s="13">
         <v>8.6</v>
       </c>
-      <c r="R96">
+      <c r="R96" s="13">
         <v>0.4</v>
       </c>
-      <c r="S96" s="1">
+      <c r="S96" s="13">
         <v>1.9E-2</v>
       </c>
-      <c r="T96" s="1">
+      <c r="T96" s="13">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="U96">
+      <c r="U96" s="13">
         <v>2</v>
       </c>
-      <c r="V96">
+      <c r="V96" s="13">
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A97" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C97">
         <v>8012</v>
       </c>
@@ -3044,7 +3069,7 @@
       <c r="J97">
         <v>0.18</v>
       </c>
-      <c r="K97">
+      <c r="K97" s="7">
         <v>0.58599999999999997</v>
       </c>
       <c r="L97">
@@ -3081,7 +3106,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A98" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C98">
         <v>53003</v>
       </c>
@@ -3106,7 +3134,7 @@
       <c r="J98">
         <v>1</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="7">
         <v>0.39</v>
       </c>
       <c r="L98">
@@ -3143,7 +3171,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A99" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C99">
         <v>26007</v>
       </c>
@@ -3168,7 +3199,7 @@
       <c r="J99">
         <v>0.4</v>
       </c>
-      <c r="K99">
+      <c r="K99" s="7">
         <v>0.27700000000000002</v>
       </c>
       <c r="L99">
@@ -3205,7 +3236,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A100" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C100">
         <v>20010</v>
       </c>
@@ -3230,7 +3264,7 @@
       <c r="J100">
         <v>2.4</v>
       </c>
-      <c r="K100">
+      <c r="K100" s="7">
         <v>0.53</v>
       </c>
       <c r="L100">
@@ -3267,7 +3301,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C101">
         <v>66016</v>
       </c>
@@ -3292,7 +3329,7 @@
       <c r="J101">
         <v>0.3</v>
       </c>
-      <c r="K101">
+      <c r="K101" s="7">
         <v>0.19</v>
       </c>
       <c r="L101">
@@ -3329,7 +3366,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C102">
         <v>34006</v>
       </c>
@@ -3354,7 +3394,7 @@
       <c r="J102">
         <v>0.4</v>
       </c>
-      <c r="K102">
+      <c r="K102" s="7">
         <v>0.24</v>
       </c>
       <c r="L102">
@@ -3391,7 +3431,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A103" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C103">
         <v>8007</v>
       </c>
@@ -3416,7 +3459,7 @@
       <c r="J103">
         <v>0.12</v>
       </c>
-      <c r="K103">
+      <c r="K103" s="7">
         <v>0.22</v>
       </c>
       <c r="L103">
@@ -3453,7 +3496,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A104" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C104">
         <v>36043</v>
       </c>
@@ -3478,7 +3524,7 @@
       <c r="J104">
         <v>0.3</v>
       </c>
-      <c r="K104">
+      <c r="K104" s="7">
         <v>0.09</v>
       </c>
       <c r="L104">
@@ -3515,7 +3561,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A105" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C105">
         <v>54027</v>
       </c>
@@ -3540,7 +3589,7 @@
       <c r="J105">
         <v>0.3</v>
       </c>
-      <c r="K105">
+      <c r="K105" s="7">
         <v>0.55000000000000004</v>
       </c>
       <c r="L105">
@@ -3577,7 +3626,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C106">
         <v>22020</v>
       </c>
@@ -3602,7 +3654,7 @@
       <c r="J106">
         <v>0.3</v>
       </c>
-      <c r="K106">
+      <c r="K106" s="7">
         <v>0.14000000000000001</v>
       </c>
       <c r="L106">
@@ -3639,7 +3691,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A107" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C107">
         <v>24004</v>
       </c>
@@ -3664,7 +3719,7 @@
       <c r="J107">
         <v>0.4</v>
       </c>
-      <c r="K107">
+      <c r="K107" s="7">
         <v>0.501</v>
       </c>
       <c r="L107">
@@ -3701,7 +3756,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C108">
         <v>24031</v>
       </c>
@@ -3726,7 +3784,7 @@
       <c r="J108">
         <v>0.3</v>
       </c>
-      <c r="K108">
+      <c r="K108" s="7">
         <v>0.32300000000000001</v>
       </c>
       <c r="L108">
@@ -3763,7 +3821,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A109" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="C109">
         <v>30008</v>
       </c>
@@ -3788,7 +3849,7 @@
       <c r="J109">
         <v>0.23</v>
       </c>
-      <c r="K109">
+      <c r="K109" s="7">
         <v>0.46</v>
       </c>
       <c r="L109">
@@ -3825,7 +3886,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C110">
         <v>6004</v>
       </c>
@@ -3850,7 +3911,7 @@
       <c r="J110">
         <v>0.3</v>
       </c>
-      <c r="K110">
+      <c r="K110" s="7">
         <v>0.16200000000000001</v>
       </c>
       <c r="L110">
@@ -3887,7 +3948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C111">
         <v>20013</v>
       </c>
@@ -3912,7 +3973,7 @@
       <c r="J111">
         <v>0.3</v>
       </c>
-      <c r="K111">
+      <c r="K111" s="7">
         <v>0.45400000000000001</v>
       </c>
       <c r="L111">
@@ -3949,7 +4010,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C112">
         <v>17025</v>
       </c>
@@ -3974,7 +4035,7 @@
       <c r="J112">
         <v>0.3</v>
       </c>
-      <c r="K112">
+      <c r="K112" s="7">
         <v>0.28000000000000003</v>
       </c>
       <c r="L112">
@@ -4036,7 +4097,7 @@
       <c r="J113">
         <v>1.3</v>
       </c>
-      <c r="K113">
+      <c r="K113" s="7">
         <v>0.52</v>
       </c>
       <c r="L113">
@@ -4098,7 +4159,7 @@
       <c r="J114">
         <v>0.17</v>
       </c>
-      <c r="K114">
+      <c r="K114" s="7">
         <v>0.32</v>
       </c>
       <c r="L114">
@@ -4160,7 +4221,7 @@
       <c r="J115">
         <v>0.8</v>
       </c>
-      <c r="K115">
+      <c r="K115" s="7">
         <v>0.69099999999999995</v>
       </c>
       <c r="L115">
@@ -4222,7 +4283,7 @@
       <c r="J116">
         <v>0.7</v>
       </c>
-      <c r="K116">
+      <c r="K116" s="7">
         <v>0.65</v>
       </c>
       <c r="L116">
@@ -4284,7 +4345,7 @@
       <c r="J117">
         <v>10</v>
       </c>
-      <c r="K117">
+      <c r="K117" s="7">
         <v>0.92</v>
       </c>
       <c r="L117">
@@ -4346,7 +4407,7 @@
       <c r="J118">
         <v>0.3</v>
       </c>
-      <c r="K118">
+      <c r="K118" s="7">
         <v>0.58499999999999996</v>
       </c>
       <c r="L118">
@@ -4408,7 +4469,7 @@
       <c r="J119">
         <v>0.25</v>
       </c>
-      <c r="K119">
+      <c r="K119" s="7">
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="L119">
@@ -4470,7 +4531,7 @@
       <c r="J120">
         <v>0.21</v>
       </c>
-      <c r="K120">
+      <c r="K120" s="7">
         <v>0.31</v>
       </c>
       <c r="L120">
@@ -4532,7 +4593,7 @@
       <c r="J121">
         <v>0.7</v>
       </c>
-      <c r="K121">
+      <c r="K121" s="7">
         <v>0.43</v>
       </c>
       <c r="L121">
@@ -4594,7 +4655,7 @@
       <c r="J122">
         <v>0.7</v>
       </c>
-      <c r="K122">
+      <c r="K122" s="7">
         <v>0.11</v>
       </c>
       <c r="L122">
@@ -4656,7 +4717,7 @@
       <c r="J123">
         <v>0.4</v>
       </c>
-      <c r="K123">
+      <c r="K123" s="7">
         <v>0.16</v>
       </c>
       <c r="L123">
@@ -4718,7 +4779,7 @@
       <c r="J124">
         <v>1.8</v>
       </c>
-      <c r="K124">
+      <c r="K124" s="7">
         <v>0.71</v>
       </c>
       <c r="L124">
@@ -4780,7 +4841,7 @@
       <c r="J125">
         <v>0.4</v>
       </c>
-      <c r="K125">
+      <c r="K125" s="7">
         <v>0.54</v>
       </c>
       <c r="L125">
@@ -4842,7 +4903,7 @@
       <c r="J126">
         <v>0.4</v>
       </c>
-      <c r="K126">
+      <c r="K126" s="7">
         <v>0.47</v>
       </c>
       <c r="L126">
@@ -4904,7 +4965,7 @@
       <c r="J127">
         <v>0.17</v>
       </c>
-      <c r="K127">
+      <c r="K127" s="7">
         <v>0.498</v>
       </c>
       <c r="L127">
@@ -4966,7 +5027,7 @@
       <c r="J128">
         <v>0.3</v>
       </c>
-      <c r="K128">
+      <c r="K128" s="7">
         <v>0.26</v>
       </c>
       <c r="L128">
@@ -5028,7 +5089,7 @@
       <c r="J129">
         <v>0.4</v>
       </c>
-      <c r="K129">
+      <c r="K129" s="7">
         <v>0.71399999999999997</v>
       </c>
       <c r="L129">
@@ -5090,7 +5151,7 @@
       <c r="J130">
         <v>6</v>
       </c>
-      <c r="K130">
+      <c r="K130" s="7">
         <v>0.64</v>
       </c>
       <c r="L130">
@@ -5152,7 +5213,7 @@
       <c r="J131">
         <v>7</v>
       </c>
-      <c r="K131">
+      <c r="K131" s="7">
         <v>0.68</v>
       </c>
       <c r="L131">
@@ -5214,7 +5275,7 @@
       <c r="J132">
         <v>0.23</v>
       </c>
-      <c r="K132">
+      <c r="K132" s="7">
         <v>0.22600000000000001</v>
       </c>
       <c r="L132">
@@ -5276,7 +5337,7 @@
       <c r="J133">
         <v>0.5</v>
       </c>
-      <c r="K133">
+      <c r="K133" s="7">
         <v>0.13</v>
       </c>
       <c r="L133">
@@ -5338,7 +5399,7 @@
       <c r="J134">
         <v>0.2</v>
       </c>
-      <c r="K134">
+      <c r="K134" s="7">
         <v>0.30199999999999999</v>
       </c>
       <c r="L134">
@@ -5400,7 +5461,7 @@
       <c r="J135">
         <v>0.8</v>
       </c>
-      <c r="K135">
+      <c r="K135" s="7">
         <v>0.26</v>
       </c>
       <c r="L135">
@@ -5462,7 +5523,7 @@
       <c r="J136">
         <v>0.7</v>
       </c>
-      <c r="K136">
+      <c r="K136" s="7">
         <v>0.55000000000000004</v>
       </c>
       <c r="L136">
@@ -5524,7 +5585,7 @@
       <c r="J137">
         <v>0.4</v>
       </c>
-      <c r="K137">
+      <c r="K137" s="7">
         <v>0.35</v>
       </c>
       <c r="L137">
@@ -5586,7 +5647,7 @@
       <c r="J138">
         <v>0.3</v>
       </c>
-      <c r="K138">
+      <c r="K138" s="7">
         <v>0.7</v>
       </c>
       <c r="L138">
@@ -5648,7 +5709,7 @@
       <c r="J139">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K139">
+      <c r="K139" s="7">
         <v>0.77</v>
       </c>
       <c r="L139">
@@ -5710,7 +5771,7 @@
       <c r="J140">
         <v>0.13</v>
       </c>
-      <c r="K140">
+      <c r="K140" s="7">
         <v>0.06</v>
       </c>
       <c r="L140">
@@ -5772,7 +5833,7 @@
       <c r="J141">
         <v>0.18</v>
       </c>
-      <c r="K141">
+      <c r="K141" s="7">
         <v>0.24</v>
       </c>
       <c r="L141">
@@ -5834,7 +5895,7 @@
       <c r="J142">
         <v>0.4</v>
       </c>
-      <c r="K142">
+      <c r="K142" s="7">
         <v>0.48</v>
       </c>
       <c r="L142">
@@ -5896,7 +5957,7 @@
       <c r="J143">
         <v>0.24</v>
       </c>
-      <c r="K143">
+      <c r="K143" s="7">
         <v>0.39</v>
       </c>
       <c r="L143">
@@ -5958,7 +6019,7 @@
       <c r="J144">
         <v>0.4</v>
       </c>
-      <c r="K144">
+      <c r="K144" s="7">
         <v>0.38</v>
       </c>
       <c r="L144">
@@ -6020,7 +6081,7 @@
       <c r="J145">
         <v>0.19</v>
       </c>
-      <c r="K145">
+      <c r="K145" s="7">
         <v>0.16</v>
       </c>
       <c r="L145">
@@ -6082,7 +6143,7 @@
       <c r="J146">
         <v>0.16</v>
       </c>
-      <c r="K146">
+      <c r="K146" s="7">
         <v>0.24</v>
       </c>
       <c r="L146">
@@ -6144,7 +6205,7 @@
       <c r="J147">
         <v>0.4</v>
       </c>
-      <c r="K147">
+      <c r="K147" s="7">
         <v>0.59</v>
       </c>
       <c r="L147">
@@ -6206,7 +6267,7 @@
       <c r="J148">
         <v>0.5</v>
       </c>
-      <c r="K148">
+      <c r="K148" s="7">
         <v>0.37</v>
       </c>
       <c r="L148">
@@ -6268,7 +6329,7 @@
       <c r="J149">
         <v>3</v>
       </c>
-      <c r="K149">
+      <c r="K149" s="7">
         <v>0.23</v>
       </c>
       <c r="L149">
@@ -6330,7 +6391,7 @@
       <c r="J150">
         <v>0.2</v>
       </c>
-      <c r="K150">
+      <c r="K150" s="7">
         <v>0.39</v>
       </c>
       <c r="L150">
@@ -6392,7 +6453,7 @@
       <c r="J151">
         <v>0.6</v>
       </c>
-      <c r="K151">
+      <c r="K151" s="7">
         <v>0.72</v>
       </c>
       <c r="L151">
@@ -6454,7 +6515,7 @@
       <c r="J152">
         <v>0.25</v>
       </c>
-      <c r="K152">
+      <c r="K152" s="7">
         <v>0.08</v>
       </c>
       <c r="L152">
@@ -6516,7 +6577,7 @@
       <c r="J153">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K153">
+      <c r="K153" s="7">
         <v>0.1</v>
       </c>
       <c r="L153">
@@ -6578,7 +6639,7 @@
       <c r="J154">
         <v>0.11</v>
       </c>
-      <c r="K154">
+      <c r="K154" s="7">
         <v>0.60799999999999998</v>
       </c>
       <c r="L154">
@@ -6640,7 +6701,7 @@
       <c r="J155">
         <v>0.3</v>
       </c>
-      <c r="K155">
+      <c r="K155" s="7">
         <v>0.67</v>
       </c>
       <c r="L155">

--- a/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
+++ b/data/Milliman_et_al_2014_WIYN_single_lined_orbits.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="104">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t xml:space="preserve">stampede</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check if solved</t>
   </si>
 </sst>
 </file>
@@ -494,7 +497,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -555,15 +558,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -576,14 +571,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1277,7 +1264,6 @@
       <c r="A79" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B79" s="15"/>
       <c r="C79" s="0" t="n">
         <v>49002</v>
       </c>
@@ -1326,10 +1312,10 @@
       <c r="R79" s="0" t="n">
         <v>0.03</v>
       </c>
-      <c r="S79" s="16" t="n">
+      <c r="S79" s="15" t="n">
         <v>0.0259</v>
       </c>
-      <c r="T79" s="16" t="n">
+      <c r="T79" s="15" t="n">
         <v>0.0017</v>
       </c>
       <c r="U79" s="0" t="n">
@@ -1339,73 +1325,71 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" s="18" customFormat="true" ht="16" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="15"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="18" t="n">
+    <row r="80" s="16" customFormat="true" ht="16" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0"/>
+      <c r="C80" s="16" t="n">
         <v>14008</v>
       </c>
-      <c r="D80" s="18" t="n">
+      <c r="D80" s="16" t="n">
         <v>1.71953</v>
       </c>
-      <c r="E80" s="18" t="n">
+      <c r="E80" s="16" t="n">
         <v>2.4E-005</v>
       </c>
-      <c r="F80" s="18" t="n">
+      <c r="F80" s="16" t="n">
         <v>860</v>
       </c>
-      <c r="G80" s="18" t="n">
+      <c r="G80" s="16" t="n">
         <v>2.6</v>
       </c>
-      <c r="H80" s="18" t="n">
+      <c r="H80" s="16" t="n">
         <v>0.9</v>
       </c>
-      <c r="I80" s="18" t="n">
+      <c r="I80" s="16" t="n">
         <v>45.3</v>
       </c>
-      <c r="J80" s="18" t="n">
+      <c r="J80" s="16" t="n">
         <v>1.3</v>
       </c>
-      <c r="K80" s="19" t="n">
+      <c r="K80" s="17" t="n">
         <v>0.02</v>
       </c>
-      <c r="L80" s="18" t="n">
+      <c r="L80" s="16" t="n">
         <v>0.03</v>
       </c>
-      <c r="M80" s="18" t="n">
+      <c r="M80" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="N80" s="18" t="n">
+      <c r="N80" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="O80" s="18" t="n">
+      <c r="O80" s="16" t="n">
         <v>52959.5</v>
       </c>
-      <c r="P80" s="18" t="n">
+      <c r="P80" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q80" s="18" t="n">
+      <c r="Q80" s="16" t="n">
         <v>1.07</v>
       </c>
-      <c r="R80" s="18" t="n">
+      <c r="R80" s="16" t="n">
         <v>0.03</v>
       </c>
-      <c r="S80" s="20" t="n">
+      <c r="S80" s="18" t="n">
         <v>0.0166</v>
       </c>
-      <c r="T80" s="20" t="n">
+      <c r="T80" s="18" t="n">
         <v>0.0015</v>
       </c>
-      <c r="U80" s="18" t="n">
+      <c r="U80" s="16" t="n">
         <v>2.93</v>
       </c>
-      <c r="V80" s="18" t="n">
+      <c r="V80" s="16" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="81" s="8" customFormat="true" ht="16" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="15"/>
-      <c r="B81" s="21"/>
+      <c r="A81" s="0"/>
       <c r="C81" s="8" t="n">
         <v>32006</v>
       </c>
@@ -1471,7 +1455,6 @@
       <c r="A82" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B82" s="15"/>
       <c r="C82" s="0" t="n">
         <v>66004</v>
       </c>
@@ -1520,10 +1503,10 @@
       <c r="R82" s="0" t="n">
         <v>0.023</v>
       </c>
-      <c r="S82" s="16" t="n">
+      <c r="S82" s="15" t="n">
         <v>0.0135</v>
       </c>
-      <c r="T82" s="16" t="n">
+      <c r="T82" s="15" t="n">
         <v>0.0008</v>
       </c>
       <c r="U82" s="0" t="n">
@@ -1537,7 +1520,9 @@
       <c r="A83" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B83" s="15"/>
+      <c r="B83" s="0" t="s">
+        <v>103</v>
+      </c>
       <c r="C83" s="0" t="n">
         <v>13001</v>
       </c>
@@ -1586,10 +1571,10 @@
       <c r="R83" s="0" t="n">
         <v>0.06</v>
       </c>
-      <c r="S83" s="16" t="n">
+      <c r="S83" s="15" t="n">
         <v>0.073</v>
       </c>
-      <c r="T83" s="16" t="n">
+      <c r="T83" s="15" t="n">
         <v>0.004</v>
       </c>
       <c r="U83" s="0" t="n">
@@ -1599,67 +1584,67 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" s="18" customFormat="true" ht="16" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="15"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="18" t="n">
+    <row r="84" s="16" customFormat="true" ht="16" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0"/>
+      <c r="B84" s="0"/>
+      <c r="C84" s="16" t="n">
         <v>35025</v>
       </c>
-      <c r="D84" s="18" t="n">
+      <c r="D84" s="16" t="n">
         <v>4.64123</v>
       </c>
-      <c r="E84" s="18" t="n">
+      <c r="E84" s="16" t="n">
         <v>0.00013</v>
       </c>
-      <c r="F84" s="18" t="n">
+      <c r="F84" s="16" t="n">
         <v>199.4</v>
       </c>
-      <c r="G84" s="18" t="n">
+      <c r="G84" s="16" t="n">
         <v>2.45</v>
       </c>
-      <c r="H84" s="18" t="n">
+      <c r="H84" s="16" t="n">
         <v>0.22</v>
       </c>
-      <c r="I84" s="18" t="n">
+      <c r="I84" s="16" t="n">
         <v>39.2</v>
       </c>
-      <c r="J84" s="18" t="n">
+      <c r="J84" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K84" s="19" t="n">
+      <c r="K84" s="17" t="n">
         <v>0.208</v>
       </c>
-      <c r="L84" s="18" t="n">
+      <c r="L84" s="16" t="n">
         <v>0.012</v>
       </c>
-      <c r="M84" s="18" t="n">
+      <c r="M84" s="16" t="n">
         <v>117.2</v>
       </c>
-      <c r="N84" s="18" t="n">
+      <c r="N84" s="16" t="n">
         <v>2.4</v>
       </c>
-      <c r="O84" s="18" t="n">
+      <c r="O84" s="16" t="n">
         <v>51999.66</v>
       </c>
-      <c r="P84" s="18" t="n">
+      <c r="P84" s="16" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q84" s="18" t="n">
+      <c r="Q84" s="16" t="n">
         <v>2.45</v>
       </c>
-      <c r="R84" s="18" t="n">
+      <c r="R84" s="16" t="n">
         <v>0.03</v>
       </c>
-      <c r="S84" s="20" t="n">
+      <c r="S84" s="18" t="n">
         <v>0.0271</v>
       </c>
-      <c r="T84" s="20" t="n">
+      <c r="T84" s="18" t="n">
         <v>0.001</v>
       </c>
-      <c r="U84" s="18" t="n">
+      <c r="U84" s="16" t="n">
         <v>0.74</v>
       </c>
-      <c r="V84" s="18" t="n">
+      <c r="V84" s="16" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1667,7 +1652,6 @@
       <c r="A85" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B85" s="15"/>
       <c r="C85" s="0" t="n">
         <v>60006</v>
       </c>
@@ -1716,10 +1700,10 @@
       <c r="R85" s="0" t="n">
         <v>0.024</v>
       </c>
-      <c r="S85" s="16" t="n">
+      <c r="S85" s="15" t="n">
         <v>0.0296</v>
       </c>
-      <c r="T85" s="16" t="n">
+      <c r="T85" s="15" t="n">
         <v>0.0006</v>
       </c>
       <c r="U85" s="0" t="n">
@@ -1733,7 +1717,6 @@
       <c r="A86" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B86" s="15"/>
       <c r="C86" s="0" t="n">
         <v>57004</v>
       </c>
@@ -1782,10 +1765,10 @@
       <c r="R86" s="0" t="n">
         <v>0.03</v>
       </c>
-      <c r="S86" s="16" t="n">
+      <c r="S86" s="15" t="n">
         <v>0.0595</v>
       </c>
-      <c r="T86" s="16" t="n">
+      <c r="T86" s="15" t="n">
         <v>0.001</v>
       </c>
       <c r="U86" s="0" t="n">
@@ -1796,7 +1779,6 @@
       </c>
     </row>
     <row r="87" s="8" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="21"/>
       <c r="C87" s="8" t="n">
         <v>33002</v>
       </c>
@@ -1821,7 +1803,7 @@
       <c r="J87" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="K87" s="21" t="n">
+      <c r="K87" s="8" t="n">
         <v>0.022</v>
       </c>
       <c r="L87" s="8" t="n">
@@ -1858,75 +1840,72 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" s="23" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" s="19" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B88" s="22"/>
-      <c r="C88" s="23" t="n">
+      <c r="C88" s="19" t="n">
         <v>46013</v>
       </c>
-      <c r="D88" s="23" t="n">
+      <c r="D88" s="19" t="n">
         <v>14.2111</v>
       </c>
-      <c r="E88" s="23" t="n">
+      <c r="E88" s="19" t="n">
         <v>0.0015</v>
       </c>
-      <c r="F88" s="23" t="n">
+      <c r="F88" s="19" t="n">
         <v>105.4</v>
       </c>
-      <c r="G88" s="23" t="n">
+      <c r="G88" s="19" t="n">
         <v>2.3</v>
       </c>
-      <c r="H88" s="23" t="n">
+      <c r="H88" s="19" t="n">
         <v>0.3</v>
       </c>
-      <c r="I88" s="23" t="n">
+      <c r="I88" s="19" t="n">
         <v>10.8</v>
       </c>
-      <c r="J88" s="23" t="n">
+      <c r="J88" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="K88" s="24" t="n">
+      <c r="K88" s="20" t="n">
         <v>0.53</v>
       </c>
-      <c r="L88" s="23" t="n">
+      <c r="L88" s="19" t="n">
         <v>0.04</v>
       </c>
-      <c r="M88" s="23" t="n">
+      <c r="M88" s="19" t="n">
         <v>256</v>
       </c>
-      <c r="N88" s="23" t="n">
+      <c r="N88" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="O88" s="23" t="n">
+      <c r="O88" s="19" t="n">
         <v>51878.89</v>
       </c>
-      <c r="P88" s="23" t="n">
+      <c r="P88" s="19" t="n">
         <v>0.11</v>
       </c>
-      <c r="Q88" s="23" t="n">
+      <c r="Q88" s="19" t="n">
         <v>1.79</v>
       </c>
-      <c r="R88" s="23" t="n">
+      <c r="R88" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="S88" s="23" t="n">
+      <c r="S88" s="19" t="n">
         <v>0.00113</v>
       </c>
-      <c r="T88" s="23" t="n">
+      <c r="T88" s="19" t="n">
         <v>0.00018</v>
       </c>
-      <c r="U88" s="23" t="n">
+      <c r="U88" s="19" t="n">
         <v>1.41</v>
       </c>
-      <c r="V88" s="23" t="n">
+      <c r="V88" s="19" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="89" s="8" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="21"/>
-      <c r="B89" s="21"/>
       <c r="C89" s="8" t="n">
         <v>3002</v>
       </c>
@@ -1951,7 +1930,7 @@
       <c r="J89" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="K89" s="21" t="n">
+      <c r="K89" s="8" t="n">
         <v>0.022</v>
       </c>
       <c r="L89" s="8" t="n">
@@ -1988,7 +1967,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" s="23" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" s="19" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
         <v>102</v>
       </c>
@@ -2058,7 +2037,6 @@
       <c r="A91" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B91" s="15"/>
       <c r="C91" s="0" t="n">
         <v>59003</v>
       </c>
@@ -2107,10 +2085,10 @@
       <c r="R91" s="0" t="n">
         <v>0.11</v>
       </c>
-      <c r="S91" s="16" t="n">
+      <c r="S91" s="15" t="n">
         <v>0.0622</v>
       </c>
-      <c r="T91" s="16" t="n">
+      <c r="T91" s="15" t="n">
         <v>0.0022</v>
       </c>
       <c r="U91" s="0" t="n">
@@ -2120,7 +2098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" s="23" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" s="19" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
         <v>102</v>
       </c>
@@ -2186,7 +2164,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" s="23" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" s="19" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
         <v>102</v>
       </c>
@@ -2252,74 +2230,72 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" s="23" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" s="19" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B94" s="22"/>
-      <c r="C94" s="23" t="n">
+      <c r="C94" s="19" t="n">
         <v>35020</v>
       </c>
-      <c r="D94" s="23" t="n">
+      <c r="D94" s="19" t="n">
         <v>24.737</v>
       </c>
-      <c r="E94" s="23" t="n">
+      <c r="E94" s="19" t="n">
         <v>0.005</v>
       </c>
-      <c r="F94" s="23" t="n">
+      <c r="F94" s="19" t="n">
         <v>45.4</v>
       </c>
-      <c r="G94" s="23" t="n">
+      <c r="G94" s="19" t="n">
         <v>1.4</v>
       </c>
-      <c r="H94" s="23" t="n">
+      <c r="H94" s="19" t="n">
         <v>0.17</v>
       </c>
-      <c r="I94" s="23" t="n">
+      <c r="I94" s="19" t="n">
         <v>12.4</v>
       </c>
-      <c r="J94" s="23" t="n">
+      <c r="J94" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="K94" s="24" t="n">
+      <c r="K94" s="20" t="n">
         <v>0.36</v>
       </c>
-      <c r="L94" s="23" t="n">
+      <c r="L94" s="19" t="n">
         <v>0.03</v>
       </c>
-      <c r="M94" s="23" t="n">
+      <c r="M94" s="19" t="n">
         <v>136</v>
       </c>
-      <c r="N94" s="23" t="n">
+      <c r="N94" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="O94" s="23" t="n">
+      <c r="O94" s="19" t="n">
         <v>52042.16</v>
       </c>
-      <c r="P94" s="23" t="n">
+      <c r="P94" s="19" t="n">
         <v>0.19</v>
       </c>
-      <c r="Q94" s="23" t="n">
+      <c r="Q94" s="19" t="n">
         <v>3.93</v>
       </c>
-      <c r="R94" s="23" t="n">
+      <c r="R94" s="19" t="n">
         <v>0.15</v>
       </c>
-      <c r="S94" s="23" t="n">
+      <c r="S94" s="19" t="n">
         <v>0.004</v>
       </c>
-      <c r="T94" s="23" t="n">
+      <c r="T94" s="19" t="n">
         <v>0.0004</v>
       </c>
-      <c r="U94" s="23" t="n">
+      <c r="U94" s="19" t="n">
         <v>0.58</v>
       </c>
-      <c r="V94" s="23" t="n">
+      <c r="V94" s="19" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="95" s="8" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="21"/>
       <c r="C95" s="8" t="n">
         <v>24012</v>
       </c>
@@ -2344,7 +2320,7 @@
       <c r="J95" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="K95" s="21" t="n">
+      <c r="K95" s="8" t="n">
         <v>0.004</v>
       </c>
       <c r="L95" s="8" t="n">
@@ -2382,7 +2358,6 @@
       </c>
     </row>
     <row r="96" s="8" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="21"/>
       <c r="C96" s="8" t="n">
         <v>39013</v>
       </c>
@@ -2407,7 +2382,7 @@
       <c r="J96" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="K96" s="21" t="n">
+      <c r="K96" s="8" t="n">
         <v>0.06</v>
       </c>
       <c r="L96" s="8" t="n">
@@ -2562,10 +2537,10 @@
       <c r="R98" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="S98" s="16" t="n">
+      <c r="S98" s="15" t="n">
         <v>0.0005</v>
       </c>
-      <c r="T98" s="16" t="n">
+      <c r="T98" s="15" t="n">
         <v>0.0003</v>
       </c>
       <c r="U98" s="0" t="n">
@@ -2693,10 +2668,10 @@
       <c r="R100" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="S100" s="16" t="n">
+      <c r="S100" s="15" t="n">
         <v>0.013</v>
       </c>
-      <c r="T100" s="16" t="n">
+      <c r="T100" s="15" t="n">
         <v>0.006</v>
       </c>
       <c r="U100" s="0" t="n">
@@ -2758,10 +2733,10 @@
       <c r="R101" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="S101" s="16" t="n">
+      <c r="S101" s="15" t="n">
         <v>0.0451</v>
       </c>
-      <c r="T101" s="16" t="n">
+      <c r="T101" s="15" t="n">
         <v>0.0022</v>
       </c>
       <c r="U101" s="0" t="n">
@@ -3021,10 +2996,10 @@
       <c r="R105" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="S105" s="16" t="n">
+      <c r="S105" s="15" t="n">
         <v>0.0425</v>
       </c>
-      <c r="T105" s="16" t="n">
+      <c r="T105" s="15" t="n">
         <v>0.0022</v>
       </c>
       <c r="U105" s="0" t="n">
@@ -3347,10 +3322,10 @@
       <c r="R110" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="S110" s="16" t="n">
+      <c r="S110" s="15" t="n">
         <v>0.058</v>
       </c>
-      <c r="T110" s="16" t="n">
+      <c r="T110" s="15" t="n">
         <v>0.003</v>
       </c>
       <c r="U110" s="0" t="n">
@@ -3409,10 +3384,10 @@
       <c r="R111" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="S111" s="16" t="n">
+      <c r="S111" s="15" t="n">
         <v>0.0336</v>
       </c>
-      <c r="T111" s="16" t="n">
+      <c r="T111" s="15" t="n">
         <v>0.0017</v>
       </c>
       <c r="U111" s="0" t="n">
@@ -3471,10 +3446,10 @@
       <c r="R112" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="S112" s="16" t="n">
+      <c r="S112" s="15" t="n">
         <v>0.0135</v>
       </c>
-      <c r="T112" s="16" t="n">
+      <c r="T112" s="15" t="n">
         <v>0.0012</v>
       </c>
       <c r="U112" s="0" t="n">
@@ -3533,10 +3508,10 @@
       <c r="R113" s="0" t="n">
         <v>2.3</v>
       </c>
-      <c r="S113" s="16" t="n">
+      <c r="S113" s="15" t="n">
         <v>0.0033</v>
       </c>
-      <c r="T113" s="16" t="n">
+      <c r="T113" s="15" t="n">
         <v>0.0019</v>
       </c>
       <c r="U113" s="0" t="n">
@@ -3595,10 +3570,10 @@
       <c r="R114" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="S114" s="16" t="n">
+      <c r="S114" s="15" t="n">
         <v>0.00138</v>
       </c>
-      <c r="T114" s="16" t="n">
+      <c r="T114" s="15" t="n">
         <v>0.00015</v>
       </c>
       <c r="U114" s="0" t="n">
@@ -3657,10 +3632,10 @@
       <c r="R115" s="0" t="n">
         <v>1.6</v>
       </c>
-      <c r="S115" s="16" t="n">
+      <c r="S115" s="15" t="n">
         <v>0.026</v>
       </c>
-      <c r="T115" s="16" t="n">
+      <c r="T115" s="15" t="n">
         <v>0.004</v>
       </c>
       <c r="U115" s="0" t="n">
@@ -3719,10 +3694,10 @@
       <c r="R116" s="0" t="n">
         <v>1.4</v>
       </c>
-      <c r="S116" s="16" t="n">
+      <c r="S116" s="15" t="n">
         <v>0.0015</v>
       </c>
-      <c r="T116" s="16" t="n">
+      <c r="T116" s="15" t="n">
         <v>0.0006</v>
       </c>
       <c r="U116" s="0" t="n">
@@ -3781,10 +3756,10 @@
       <c r="R117" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="S117" s="16" t="n">
+      <c r="S117" s="15" t="n">
         <v>0.0077</v>
       </c>
-      <c r="T117" s="16" t="n">
+      <c r="T117" s="15" t="n">
         <v>0.014</v>
       </c>
       <c r="U117" s="0" t="n">
@@ -3843,10 +3818,10 @@
       <c r="R118" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="S118" s="16" t="n">
+      <c r="S118" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="T118" s="16" t="n">
+      <c r="T118" s="15" t="n">
         <v>0.005</v>
       </c>
       <c r="U118" s="0" t="n">
@@ -3905,10 +3880,10 @@
       <c r="R119" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="S119" s="16" t="n">
+      <c r="S119" s="15" t="n">
         <v>0.071</v>
       </c>
-      <c r="T119" s="16" t="n">
+      <c r="T119" s="15" t="n">
         <v>0.004</v>
       </c>
       <c r="U119" s="0" t="n">
@@ -3967,10 +3942,10 @@
       <c r="R120" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="S120" s="16" t="n">
+      <c r="S120" s="15" t="n">
         <v>0.0017</v>
       </c>
-      <c r="T120" s="16" t="n">
+      <c r="T120" s="15" t="n">
         <v>0.0003</v>
       </c>
       <c r="U120" s="0" t="n">
@@ -4029,10 +4004,10 @@
       <c r="R121" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="S121" s="16" t="n">
+      <c r="S121" s="15" t="n">
         <v>0.009</v>
       </c>
-      <c r="T121" s="16" t="n">
+      <c r="T121" s="15" t="n">
         <v>0.003</v>
       </c>
       <c r="U121" s="0" t="n">
@@ -4091,10 +4066,10 @@
       <c r="R122" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="S122" s="16" t="n">
+      <c r="S122" s="15" t="n">
         <v>0.079</v>
       </c>
-      <c r="T122" s="16" t="n">
+      <c r="T122" s="15" t="n">
         <v>0.013</v>
       </c>
       <c r="U122" s="0" t="n">
@@ -4153,10 +4128,10 @@
       <c r="R123" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="S123" s="16" t="n">
+      <c r="S123" s="15" t="n">
         <v>0.0083</v>
       </c>
-      <c r="T123" s="16" t="n">
+      <c r="T123" s="15" t="n">
         <v>0.0016</v>
       </c>
       <c r="U123" s="0" t="n">
@@ -4215,10 +4190,10 @@
       <c r="R124" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="S124" s="16" t="n">
+      <c r="S124" s="15" t="n">
         <v>0.034</v>
       </c>
-      <c r="T124" s="16" t="n">
+      <c r="T124" s="15" t="n">
         <v>0.015</v>
       </c>
       <c r="U124" s="0" t="n">
@@ -4277,10 +4252,10 @@
       <c r="R125" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="S125" s="16" t="n">
+      <c r="S125" s="15" t="n">
         <v>0.015</v>
       </c>
-      <c r="T125" s="16" t="n">
+      <c r="T125" s="15" t="n">
         <v>0.003</v>
       </c>
       <c r="U125" s="0" t="n">
@@ -4339,10 +4314,10 @@
       <c r="R126" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="S126" s="16" t="n">
+      <c r="S126" s="15" t="n">
         <v>0.00017</v>
       </c>
-      <c r="T126" s="16" t="n">
+      <c r="T126" s="15" t="n">
         <v>0.00012</v>
       </c>
       <c r="U126" s="0" t="n">
@@ -4401,10 +4376,10 @@
       <c r="R127" s="0" t="n">
         <v>1.3</v>
       </c>
-      <c r="S127" s="16" t="n">
+      <c r="S127" s="15" t="n">
         <v>0.0349</v>
       </c>
-      <c r="T127" s="16" t="n">
+      <c r="T127" s="15" t="n">
         <v>0.0019</v>
       </c>
       <c r="U127" s="0" t="n">
@@ -4463,10 +4438,10 @@
       <c r="R128" s="0" t="n">
         <v>2.1</v>
       </c>
-      <c r="S128" s="16" t="n">
+      <c r="S128" s="15" t="n">
         <v>0.0082</v>
       </c>
-      <c r="T128" s="16" t="n">
+      <c r="T128" s="15" t="n">
         <v>0.0012</v>
       </c>
       <c r="U128" s="0" t="n">
@@ -4525,10 +4500,10 @@
       <c r="R129" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="S129" s="16" t="n">
+      <c r="S129" s="15" t="n">
         <v>0.025</v>
       </c>
-      <c r="T129" s="16" t="n">
+      <c r="T129" s="15" t="n">
         <v>0.003</v>
       </c>
       <c r="U129" s="0" t="n">
@@ -4587,10 +4562,10 @@
       <c r="R130" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="S130" s="16" t="n">
+      <c r="S130" s="15" t="n">
         <v>0.11</v>
       </c>
-      <c r="T130" s="16" t="n">
+      <c r="T130" s="15" t="n">
         <v>0.12</v>
       </c>
       <c r="U130" s="0" t="n">
@@ -4649,10 +4624,10 @@
       <c r="R131" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="S131" s="16" t="n">
+      <c r="S131" s="15" t="n">
         <v>10.9</v>
       </c>
-      <c r="T131" s="16" t="n">
+      <c r="T131" s="15" t="n">
         <v>0.011</v>
       </c>
       <c r="U131" s="0" t="n">
@@ -4711,10 +4686,10 @@
       <c r="R132" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="S132" s="16" t="n">
+      <c r="S132" s="15" t="n">
         <v>0.621</v>
       </c>
-      <c r="T132" s="16" t="n">
+      <c r="T132" s="15" t="n">
         <v>0.02</v>
       </c>
       <c r="U132" s="0" t="n">
@@ -4773,10 +4748,10 @@
       <c r="R133" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="S133" s="16" t="n">
+      <c r="S133" s="15" t="n">
         <v>0.027</v>
       </c>
-      <c r="T133" s="16" t="n">
+      <c r="T133" s="15" t="n">
         <v>0.006</v>
       </c>
       <c r="U133" s="0" t="n">
@@ -4835,10 +4810,10 @@
       <c r="R134" s="0" t="n">
         <v>2.1</v>
       </c>
-      <c r="S134" s="16" t="n">
+      <c r="S134" s="15" t="n">
         <v>0.0241</v>
       </c>
-      <c r="T134" s="16" t="n">
+      <c r="T134" s="15" t="n">
         <v>0.0021</v>
       </c>
       <c r="U134" s="0" t="n">
@@ -4897,10 +4872,10 @@
       <c r="R135" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="S135" s="16" t="n">
+      <c r="S135" s="15" t="n">
         <v>0.66</v>
       </c>
-      <c r="T135" s="16" t="n">
+      <c r="T135" s="15" t="n">
         <v>0.08</v>
       </c>
       <c r="U135" s="0" t="n">
@@ -4959,10 +4934,10 @@
       <c r="R136" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="S136" s="16" t="n">
+      <c r="S136" s="15" t="n">
         <v>0.026</v>
       </c>
-      <c r="T136" s="16" t="n">
+      <c r="T136" s="15" t="n">
         <v>0.007</v>
       </c>
       <c r="U136" s="0" t="n">
@@ -5021,10 +4996,10 @@
       <c r="R137" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="S137" s="16" t="n">
+      <c r="S137" s="15" t="n">
         <v>0.0066</v>
       </c>
-      <c r="T137" s="16" t="n">
+      <c r="T137" s="15" t="n">
         <v>0.0018</v>
       </c>
       <c r="U137" s="0" t="n">
@@ -5083,10 +5058,10 @@
       <c r="R138" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="S138" s="16" t="n">
+      <c r="S138" s="15" t="n">
         <v>0.0172</v>
       </c>
-      <c r="T138" s="16" t="n">
+      <c r="T138" s="15" t="n">
         <v>0.0025</v>
       </c>
       <c r="U138" s="0" t="n">
@@ -5145,10 +5120,10 @@
       <c r="R139" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="S139" s="16" t="n">
+      <c r="S139" s="15" t="n">
         <v>0.003</v>
       </c>
-      <c r="T139" s="16" t="n">
+      <c r="T139" s="15" t="n">
         <v>0.003</v>
       </c>
       <c r="U139" s="0" t="n">
@@ -5207,10 +5182,10 @@
       <c r="R140" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="S140" s="16" t="n">
+      <c r="S140" s="15" t="n">
         <v>0.0201</v>
       </c>
-      <c r="T140" s="16" t="n">
+      <c r="T140" s="15" t="n">
         <v>0.0015</v>
       </c>
       <c r="U140" s="0" t="n">
@@ -5269,10 +5244,10 @@
       <c r="R141" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="S141" s="16" t="n">
+      <c r="S141" s="15" t="n">
         <v>0.0225</v>
       </c>
-      <c r="T141" s="16" t="n">
+      <c r="T141" s="15" t="n">
         <v>0.0022</v>
       </c>
       <c r="U141" s="0" t="n">
@@ -5331,10 +5306,10 @@
       <c r="R142" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="S142" s="16" t="n">
+      <c r="S142" s="15" t="n">
         <v>0.0066</v>
       </c>
-      <c r="T142" s="16" t="n">
+      <c r="T142" s="15" t="n">
         <v>0.0022</v>
       </c>
       <c r="U142" s="0" t="n">
@@ -5393,10 +5368,10 @@
       <c r="R143" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="S143" s="16" t="n">
+      <c r="S143" s="15" t="n">
         <v>0.0079</v>
       </c>
-      <c r="T143" s="16" t="n">
+      <c r="T143" s="15" t="n">
         <v>0.0015</v>
       </c>
       <c r="U143" s="0" t="n">
@@ -5455,10 +5430,10 @@
       <c r="R144" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="S144" s="16" t="n">
+      <c r="S144" s="15" t="n">
         <v>0.015</v>
       </c>
-      <c r="T144" s="16" t="n">
+      <c r="T144" s="15" t="n">
         <v>0.004</v>
       </c>
       <c r="U144" s="0" t="n">
@@ -5517,10 +5492,10 @@
       <c r="R145" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="S145" s="16" t="n">
+      <c r="S145" s="15" t="n">
         <v>0.0098</v>
       </c>
-      <c r="T145" s="16" t="n">
+      <c r="T145" s="15" t="n">
         <v>0.0016</v>
       </c>
       <c r="U145" s="0" t="n">
@@ -5579,10 +5554,10 @@
       <c r="R146" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="S146" s="16" t="n">
+      <c r="S146" s="15" t="n">
         <v>0.043</v>
       </c>
-      <c r="T146" s="16" t="n">
+      <c r="T146" s="15" t="n">
         <v>0.004</v>
       </c>
       <c r="U146" s="0" t="n">
@@ -5641,10 +5616,10 @@
       <c r="R147" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="S147" s="16" t="n">
+      <c r="S147" s="15" t="n">
         <v>0.022</v>
       </c>
-      <c r="T147" s="16" t="n">
+      <c r="T147" s="15" t="n">
         <v>0.005</v>
       </c>
       <c r="U147" s="0" t="n">
@@ -5703,10 +5678,10 @@
       <c r="R148" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="S148" s="16" t="n">
+      <c r="S148" s="15" t="n">
         <v>0.106</v>
       </c>
-      <c r="T148" s="16" t="n">
+      <c r="T148" s="15" t="n">
         <v>0.022</v>
       </c>
       <c r="U148" s="0" t="n">
@@ -5765,10 +5740,10 @@
       <c r="R149" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="S149" s="16" t="n">
+      <c r="S149" s="15" t="n">
         <v>0.2</v>
       </c>
-      <c r="T149" s="16" t="n">
+      <c r="T149" s="15" t="n">
         <v>0.19</v>
       </c>
       <c r="U149" s="0" t="n">
@@ -5827,10 +5802,10 @@
       <c r="R150" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="S150" s="16" t="n">
+      <c r="S150" s="15" t="n">
         <v>0.051</v>
       </c>
-      <c r="T150" s="16" t="n">
+      <c r="T150" s="15" t="n">
         <v>0.005</v>
       </c>
       <c r="U150" s="0" t="n">
@@ -5889,10 +5864,10 @@
       <c r="R151" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="S151" s="16" t="n">
+      <c r="S151" s="15" t="n">
         <v>0.012</v>
       </c>
-      <c r="T151" s="16" t="n">
+      <c r="T151" s="15" t="n">
         <v>0.005</v>
       </c>
       <c r="U151" s="0" t="n">
@@ -5951,10 +5926,10 @@
       <c r="R152" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="S152" s="16" t="n">
+      <c r="S152" s="15" t="n">
         <v>0.011</v>
       </c>
-      <c r="T152" s="16" t="n">
+      <c r="T152" s="15" t="n">
         <v>0.003</v>
       </c>
       <c r="U152" s="0" t="n">
@@ -6013,10 +5988,10 @@
       <c r="R153" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="S153" s="16" t="n">
+      <c r="S153" s="15" t="n">
         <v>0.022</v>
       </c>
-      <c r="T153" s="16" t="n">
+      <c r="T153" s="15" t="n">
         <v>0.003</v>
       </c>
       <c r="U153" s="0" t="n">
@@ -6075,10 +6050,10 @@
       <c r="R154" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="S154" s="16" t="n">
+      <c r="S154" s="15" t="n">
         <v>0.0299</v>
       </c>
-      <c r="T154" s="16" t="n">
+      <c r="T154" s="15" t="n">
         <v>0.0023</v>
       </c>
       <c r="U154" s="0" t="n">
@@ -6137,10 +6112,10 @@
       <c r="R155" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="S155" s="16" t="n">
+      <c r="S155" s="15" t="n">
         <v>0.019</v>
       </c>
-      <c r="T155" s="16" t="n">
+      <c r="T155" s="15" t="n">
         <v>0.004</v>
       </c>
       <c r="U155" s="0" t="n">
